--- a/Documentacion/NESUB_Desglose_Producción_Layout_V004.xlsx
+++ b/Documentacion/NESUB_Desglose_Producción_Layout_V004.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\GitHub\Animacion3D_Cortometraje_NoEraSoloUnBoton\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7F8ACC-9C49-4A5D-AD31-8D10320EBF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544C2257-101C-46B1-B339-FF165CE46602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1996,21 +1996,72 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2030,59 +2081,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2091,13 +2089,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2124,9 +2127,6 @@
     <xf numFmtId="164" fontId="0" fillId="10" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2508,29 +2508,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.4">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
-      <c r="D1" s="121"/>
-      <c r="E1" s="121"/>
-      <c r="F1" s="121"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
       <c r="J1" s="100"/>
     </row>
     <row r="2" spans="1:10" ht="3" customHeight="1">
-      <c r="A2" s="144"/>
-      <c r="B2" s="121"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
+      <c r="A2" s="128"/>
+      <c r="B2" s="123"/>
+      <c r="C2" s="123"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
       <c r="J2" s="100"/>
     </row>
     <row r="3" spans="1:10" ht="26.25">
@@ -2564,13 +2564,13 @@
       <c r="J3" s="100"/>
     </row>
     <row r="4" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A4" s="120" t="s">
+      <c r="A4" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="120" t="s">
+      <c r="B4" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="122" t="s">
+      <c r="C4" s="120" t="s">
         <v>206</v>
       </c>
       <c r="D4" s="93">
@@ -2582,7 +2582,7 @@
       <c r="F4" s="104" t="s">
         <v>247</v>
       </c>
-      <c r="G4" s="129">
+      <c r="G4" s="124">
         <v>180</v>
       </c>
       <c r="H4" s="94"/>
@@ -2594,9 +2594,9 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A5" s="120"/>
-      <c r="B5" s="120"/>
-      <c r="C5" s="120"/>
+      <c r="A5" s="121"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
       <c r="D5" s="93">
         <v>3</v>
       </c>
@@ -2606,7 +2606,7 @@
       <c r="F5" s="104" t="s">
         <v>248</v>
       </c>
-      <c r="G5" s="129"/>
+      <c r="G5" s="124"/>
       <c r="H5" s="94"/>
       <c r="I5" s="94" t="s">
         <v>34</v>
@@ -2614,9 +2614,9 @@
       <c r="J5" s="100"/>
     </row>
     <row r="6" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A6" s="120"/>
-      <c r="B6" s="120"/>
-      <c r="C6" s="120"/>
+      <c r="A6" s="121"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="121"/>
       <c r="D6" s="93">
         <v>3</v>
       </c>
@@ -2626,7 +2626,7 @@
       <c r="F6" s="104" t="s">
         <v>249</v>
       </c>
-      <c r="G6" s="129"/>
+      <c r="G6" s="124"/>
       <c r="H6" s="94"/>
       <c r="I6" s="94" t="s">
         <v>34</v>
@@ -2634,9 +2634,9 @@
       <c r="J6" s="100"/>
     </row>
     <row r="7" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A7" s="120"/>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
+      <c r="A7" s="121"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="121"/>
       <c r="D7" s="93">
         <v>4</v>
       </c>
@@ -2646,7 +2646,7 @@
       <c r="F7" s="104" t="s">
         <v>250</v>
       </c>
-      <c r="G7" s="129"/>
+      <c r="G7" s="124"/>
       <c r="H7" s="94" t="s">
         <v>158</v>
       </c>
@@ -2656,9 +2656,9 @@
       <c r="J7" s="100"/>
     </row>
     <row r="8" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A8" s="121"/>
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
+      <c r="A8" s="123"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="123"/>
       <c r="D8" s="93">
         <v>5</v>
       </c>
@@ -2668,7 +2668,7 @@
       <c r="F8" s="104" t="s">
         <v>187</v>
       </c>
-      <c r="G8" s="121"/>
+      <c r="G8" s="123"/>
       <c r="H8" s="94"/>
       <c r="I8" s="94" t="s">
         <v>34</v>
@@ -2676,25 +2676,25 @@
       <c r="J8" s="100"/>
     </row>
     <row r="9" spans="1:10" ht="14.25">
-      <c r="A9" s="142"/>
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
+      <c r="A9" s="126"/>
+      <c r="B9" s="123"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="123"/>
+      <c r="G9" s="123"/>
+      <c r="H9" s="123"/>
+      <c r="I9" s="123"/>
       <c r="J9" s="100"/>
     </row>
     <row r="10" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="120" t="s">
+      <c r="B10" s="121" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="120" t="s">
+      <c r="C10" s="121" t="s">
         <v>160</v>
       </c>
       <c r="D10" s="93">
@@ -2706,7 +2706,7 @@
       <c r="F10" s="94" t="s">
         <v>250</v>
       </c>
-      <c r="G10" s="129">
+      <c r="G10" s="124">
         <v>60</v>
       </c>
       <c r="H10" s="94"/>
@@ -2718,9 +2718,9 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
+      <c r="A11" s="121"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
       <c r="D11" s="93">
         <v>2</v>
       </c>
@@ -2730,7 +2730,7 @@
       <c r="F11" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="G11" s="129"/>
+      <c r="G11" s="124"/>
       <c r="H11" s="94" t="s">
         <v>159</v>
       </c>
@@ -2740,25 +2740,25 @@
       <c r="J11" s="100"/>
     </row>
     <row r="12" spans="1:10" ht="14.25">
-      <c r="A12" s="142"/>
-      <c r="B12" s="121"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="121"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="121"/>
-      <c r="I12" s="121"/>
+      <c r="A12" s="126"/>
+      <c r="B12" s="123"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="123"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
       <c r="J12" s="100"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
-      <c r="A13" s="120" t="s">
+      <c r="A13" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="120" t="s">
+      <c r="B13" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="122" t="s">
+      <c r="C13" s="120" t="s">
         <v>205</v>
       </c>
       <c r="D13" s="93">
@@ -2770,7 +2770,7 @@
       <c r="F13" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="G13" s="137">
+      <c r="G13" s="122">
         <v>120</v>
       </c>
       <c r="H13" s="94" t="s">
@@ -2784,9 +2784,9 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="21" customHeight="1">
-      <c r="A14" s="120"/>
-      <c r="B14" s="120"/>
-      <c r="C14" s="120"/>
+      <c r="A14" s="121"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="121"/>
       <c r="D14" s="93">
         <v>2</v>
       </c>
@@ -2796,7 +2796,7 @@
       <c r="F14" s="94" t="s">
         <v>250</v>
       </c>
-      <c r="G14" s="137"/>
+      <c r="G14" s="122"/>
       <c r="H14" s="94"/>
       <c r="I14" s="94" t="s">
         <v>34</v>
@@ -2804,15 +2804,15 @@
       <c r="J14" s="100"/>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A15" s="142"/>
-      <c r="B15" s="121"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
+      <c r="A15" s="126"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="123"/>
+      <c r="E15" s="123"/>
+      <c r="F15" s="123"/>
+      <c r="G15" s="123"/>
+      <c r="H15" s="123"/>
+      <c r="I15" s="123"/>
       <c r="J15" s="100"/>
     </row>
     <row r="16" spans="1:10" ht="28.5" customHeight="1">
@@ -2846,13 +2846,13 @@
       <c r="J16" s="100"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A17" s="120" t="s">
+      <c r="A17" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="120" t="s">
+      <c r="B17" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="122" t="s">
+      <c r="C17" s="120" t="s">
         <v>203</v>
       </c>
       <c r="D17" s="93">
@@ -2864,7 +2864,7 @@
       <c r="F17" s="104" t="s">
         <v>251</v>
       </c>
-      <c r="G17" s="137">
+      <c r="G17" s="122">
         <v>120</v>
       </c>
       <c r="H17" s="94" t="s">
@@ -2878,9 +2878,9 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A18" s="121"/>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
+      <c r="A18" s="123"/>
+      <c r="B18" s="123"/>
+      <c r="C18" s="123"/>
       <c r="D18" s="93">
         <v>2</v>
       </c>
@@ -2890,7 +2890,7 @@
       <c r="F18" s="104" t="s">
         <v>252</v>
       </c>
-      <c r="G18" s="121"/>
+      <c r="G18" s="123"/>
       <c r="H18" s="94"/>
       <c r="I18" s="94" t="s">
         <v>34</v>
@@ -2898,9 +2898,9 @@
       <c r="J18" s="100"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A19" s="121"/>
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
+      <c r="A19" s="123"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="123"/>
       <c r="D19" s="93">
         <v>3</v>
       </c>
@@ -2910,7 +2910,7 @@
       <c r="F19" s="104" t="s">
         <v>253</v>
       </c>
-      <c r="G19" s="121"/>
+      <c r="G19" s="123"/>
       <c r="H19" s="94"/>
       <c r="I19" s="94" t="s">
         <v>34</v>
@@ -2918,25 +2918,25 @@
       <c r="J19" s="100"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A20" s="136"/>
-      <c r="B20" s="121"/>
-      <c r="C20" s="121"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="121"/>
-      <c r="I20" s="121"/>
+      <c r="A20" s="125"/>
+      <c r="B20" s="123"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="123"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="123"/>
       <c r="J20" s="100"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A21" s="120" t="s">
+      <c r="A21" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="120" t="s">
+      <c r="B21" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="122" t="s">
+      <c r="C21" s="120" t="s">
         <v>202</v>
       </c>
       <c r="D21" s="93">
@@ -2948,7 +2948,7 @@
       <c r="F21" s="104" t="s">
         <v>254</v>
       </c>
-      <c r="G21" s="137">
+      <c r="G21" s="122">
         <v>90</v>
       </c>
       <c r="H21" s="94"/>
@@ -2960,9 +2960,9 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A22" s="121"/>
-      <c r="B22" s="121"/>
-      <c r="C22" s="121"/>
+      <c r="A22" s="123"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="123"/>
       <c r="D22" s="93">
         <v>2</v>
       </c>
@@ -2972,7 +2972,7 @@
       <c r="F22" s="94" t="s">
         <v>253</v>
       </c>
-      <c r="G22" s="121"/>
+      <c r="G22" s="123"/>
       <c r="H22" s="94"/>
       <c r="I22" s="94" t="s">
         <v>34</v>
@@ -2980,25 +2980,25 @@
       <c r="J22" s="100"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A23" s="136"/>
-      <c r="B23" s="121"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
-      <c r="G23" s="121"/>
-      <c r="H23" s="121"/>
-      <c r="I23" s="121"/>
+      <c r="A23" s="125"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="123"/>
       <c r="J23" s="100"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="120" t="s">
+      <c r="C24" s="121" t="s">
         <v>166</v>
       </c>
       <c r="D24" s="93">
@@ -3010,7 +3010,7 @@
       <c r="F24" s="94" t="s">
         <v>251</v>
       </c>
-      <c r="G24" s="137">
+      <c r="G24" s="122">
         <v>90</v>
       </c>
       <c r="H24" s="94" t="s">
@@ -3024,9 +3024,9 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A25" s="121"/>
-      <c r="B25" s="121"/>
-      <c r="C25" s="121"/>
+      <c r="A25" s="123"/>
+      <c r="B25" s="123"/>
+      <c r="C25" s="123"/>
       <c r="D25" s="93">
         <v>2</v>
       </c>
@@ -3036,7 +3036,7 @@
       <c r="F25" s="104" t="s">
         <v>255</v>
       </c>
-      <c r="G25" s="121"/>
+      <c r="G25" s="123"/>
       <c r="H25" s="94" t="s">
         <v>173</v>
       </c>
@@ -3046,25 +3046,25 @@
       <c r="J25" s="100"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A26" s="136"/>
-      <c r="B26" s="121"/>
-      <c r="C26" s="121"/>
-      <c r="D26" s="121"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="121"/>
-      <c r="G26" s="121"/>
-      <c r="H26" s="121"/>
-      <c r="I26" s="121"/>
+      <c r="A26" s="125"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="123"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
       <c r="J26" s="100"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A27" s="120" t="s">
+      <c r="A27" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="120" t="s">
+      <c r="B27" s="121" t="s">
         <v>168</v>
       </c>
-      <c r="C27" s="122" t="s">
+      <c r="C27" s="120" t="s">
         <v>204</v>
       </c>
       <c r="D27" s="93">
@@ -3076,7 +3076,7 @@
       <c r="F27" s="104" t="s">
         <v>254</v>
       </c>
-      <c r="G27" s="129">
+      <c r="G27" s="124">
         <v>90</v>
       </c>
       <c r="H27" s="94"/>
@@ -3088,9 +3088,9 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A28" s="121"/>
-      <c r="B28" s="121"/>
-      <c r="C28" s="121"/>
+      <c r="A28" s="123"/>
+      <c r="B28" s="123"/>
+      <c r="C28" s="123"/>
       <c r="D28" s="93">
         <v>2</v>
       </c>
@@ -3100,7 +3100,7 @@
       <c r="F28" s="94" t="s">
         <v>253</v>
       </c>
-      <c r="G28" s="121"/>
+      <c r="G28" s="123"/>
       <c r="H28" s="94"/>
       <c r="I28" s="94" t="s">
         <v>34</v>
@@ -3138,13 +3138,13 @@
       <c r="J29" s="100"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A30" s="120" t="s">
+      <c r="A30" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="120" t="s">
+      <c r="B30" s="121" t="s">
         <v>169</v>
       </c>
-      <c r="C30" s="122" t="s">
+      <c r="C30" s="120" t="s">
         <v>229</v>
       </c>
       <c r="D30" s="93">
@@ -3156,7 +3156,7 @@
       <c r="F30" s="104" t="s">
         <v>256</v>
       </c>
-      <c r="G30" s="129">
+      <c r="G30" s="124">
         <v>120</v>
       </c>
       <c r="H30" s="94" t="s">
@@ -3168,9 +3168,9 @@
       <c r="J30" s="100"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A31" s="121"/>
-      <c r="B31" s="121"/>
-      <c r="C31" s="121"/>
+      <c r="A31" s="123"/>
+      <c r="B31" s="123"/>
+      <c r="C31" s="123"/>
       <c r="D31" s="93">
         <v>2</v>
       </c>
@@ -3180,7 +3180,7 @@
       <c r="F31" s="104" t="s">
         <v>255</v>
       </c>
-      <c r="G31" s="121"/>
+      <c r="G31" s="123"/>
       <c r="H31" s="94" t="s">
         <v>174</v>
       </c>
@@ -3190,9 +3190,9 @@
       <c r="J31" s="100"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A32" s="121"/>
-      <c r="B32" s="121"/>
-      <c r="C32" s="121"/>
+      <c r="A32" s="123"/>
+      <c r="B32" s="123"/>
+      <c r="C32" s="123"/>
       <c r="D32" s="93">
         <v>3</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="F32" s="104" t="s">
         <v>257</v>
       </c>
-      <c r="G32" s="121"/>
+      <c r="G32" s="123"/>
       <c r="H32" s="94" t="s">
         <v>177</v>
       </c>
@@ -3212,9 +3212,9 @@
       <c r="J32" s="100"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A33" s="121"/>
-      <c r="B33" s="121"/>
-      <c r="C33" s="121"/>
+      <c r="A33" s="123"/>
+      <c r="B33" s="123"/>
+      <c r="C33" s="123"/>
       <c r="D33" s="93">
         <v>4</v>
       </c>
@@ -3224,7 +3224,7 @@
       <c r="F33" s="104" t="s">
         <v>258</v>
       </c>
-      <c r="G33" s="121"/>
+      <c r="G33" s="123"/>
       <c r="H33" s="94" t="s">
         <v>177</v>
       </c>
@@ -3234,9 +3234,9 @@
       <c r="J33" s="100"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A34" s="121"/>
-      <c r="B34" s="121"/>
-      <c r="C34" s="121"/>
+      <c r="A34" s="123"/>
+      <c r="B34" s="123"/>
+      <c r="C34" s="123"/>
       <c r="D34" s="93">
         <v>5</v>
       </c>
@@ -3246,7 +3246,7 @@
       <c r="F34" s="94" t="s">
         <v>253</v>
       </c>
-      <c r="G34" s="121"/>
+      <c r="G34" s="123"/>
       <c r="H34" s="94"/>
       <c r="I34" s="94" t="s">
         <v>34</v>
@@ -3254,9 +3254,9 @@
       <c r="J34" s="100"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A35" s="121"/>
-      <c r="B35" s="121"/>
-      <c r="C35" s="121"/>
+      <c r="A35" s="123"/>
+      <c r="B35" s="123"/>
+      <c r="C35" s="123"/>
       <c r="D35" s="93">
         <v>6</v>
       </c>
@@ -3266,7 +3266,7 @@
       <c r="F35" s="104" t="s">
         <v>188</v>
       </c>
-      <c r="G35" s="121"/>
+      <c r="G35" s="123"/>
       <c r="H35" s="94" t="s">
         <v>181</v>
       </c>
@@ -3276,9 +3276,9 @@
       <c r="J35" s="100"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A36" s="121"/>
-      <c r="B36" s="121"/>
-      <c r="C36" s="121"/>
+      <c r="A36" s="123"/>
+      <c r="B36" s="123"/>
+      <c r="C36" s="123"/>
       <c r="D36" s="95">
         <v>7</v>
       </c>
@@ -3288,7 +3288,7 @@
       <c r="F36" s="104" t="s">
         <v>189</v>
       </c>
-      <c r="G36" s="121"/>
+      <c r="G36" s="123"/>
       <c r="H36" s="94" t="s">
         <v>184</v>
       </c>
@@ -3310,13 +3310,13 @@
       <c r="J37" s="100"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A38" s="120" t="s">
+      <c r="A38" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="120" t="s">
+      <c r="B38" s="121" t="s">
         <v>179</v>
       </c>
-      <c r="C38" s="120" t="s">
+      <c r="C38" s="121" t="s">
         <v>180</v>
       </c>
       <c r="D38" s="93">
@@ -3328,7 +3328,7 @@
       <c r="F38" s="104" t="s">
         <v>256</v>
       </c>
-      <c r="G38" s="129">
+      <c r="G38" s="124">
         <v>60</v>
       </c>
       <c r="H38" s="94"/>
@@ -3338,9 +3338,9 @@
       <c r="J38" s="100"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A39" s="121"/>
-      <c r="B39" s="121"/>
-      <c r="C39" s="121"/>
+      <c r="A39" s="123"/>
+      <c r="B39" s="123"/>
+      <c r="C39" s="123"/>
       <c r="D39" s="93">
         <v>2</v>
       </c>
@@ -3350,7 +3350,7 @@
       <c r="F39" s="94" t="s">
         <v>188</v>
       </c>
-      <c r="G39" s="121"/>
+      <c r="G39" s="123"/>
       <c r="H39" s="94"/>
       <c r="I39" s="94" t="s">
         <v>34</v>
@@ -3358,9 +3358,9 @@
       <c r="J39" s="100"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A40" s="121"/>
-      <c r="B40" s="121"/>
-      <c r="C40" s="121"/>
+      <c r="A40" s="123"/>
+      <c r="B40" s="123"/>
+      <c r="C40" s="123"/>
       <c r="D40" s="93">
         <v>3</v>
       </c>
@@ -3370,7 +3370,7 @@
       <c r="F40" s="94" t="s">
         <v>253</v>
       </c>
-      <c r="G40" s="121"/>
+      <c r="G40" s="123"/>
       <c r="H40" s="94"/>
       <c r="I40" s="94" t="s">
         <v>34</v>
@@ -3390,13 +3390,13 @@
       <c r="J41" s="100"/>
     </row>
     <row r="42" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A42" s="120" t="s">
+      <c r="A42" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="B42" s="120" t="s">
+      <c r="B42" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="C42" s="122" t="s">
+      <c r="C42" s="120" t="s">
         <v>207</v>
       </c>
       <c r="D42" s="93">
@@ -3408,7 +3408,7 @@
       <c r="F42" s="104" t="s">
         <v>256</v>
       </c>
-      <c r="G42" s="129">
+      <c r="G42" s="124">
         <v>60</v>
       </c>
       <c r="H42" s="94"/>
@@ -3420,9 +3420,9 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A43" s="120"/>
-      <c r="B43" s="120"/>
-      <c r="C43" s="122"/>
+      <c r="A43" s="121"/>
+      <c r="B43" s="121"/>
+      <c r="C43" s="120"/>
       <c r="D43" s="93">
         <v>2</v>
       </c>
@@ -3432,7 +3432,7 @@
       <c r="F43" s="104" t="s">
         <v>260</v>
       </c>
-      <c r="G43" s="129"/>
+      <c r="G43" s="124"/>
       <c r="H43" s="94"/>
       <c r="I43" s="94" t="s">
         <v>34</v>
@@ -3440,9 +3440,9 @@
       <c r="J43" s="96"/>
     </row>
     <row r="44" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A44" s="120"/>
-      <c r="B44" s="120"/>
-      <c r="C44" s="120"/>
+      <c r="A44" s="121"/>
+      <c r="B44" s="121"/>
+      <c r="C44" s="121"/>
       <c r="D44" s="93">
         <v>3</v>
       </c>
@@ -3452,7 +3452,7 @@
       <c r="F44" s="104" t="s">
         <v>259</v>
       </c>
-      <c r="G44" s="129"/>
+      <c r="G44" s="124"/>
       <c r="H44" s="94"/>
       <c r="I44" s="94" t="s">
         <v>34</v>
@@ -3472,13 +3472,13 @@
       <c r="J45" s="100"/>
     </row>
     <row r="46" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A46" s="119" t="s">
+      <c r="A46" s="132" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="119" t="s">
+      <c r="B46" s="132" t="s">
         <v>222</v>
       </c>
-      <c r="C46" s="130" t="s">
+      <c r="C46" s="136" t="s">
         <v>209</v>
       </c>
       <c r="D46" s="97">
@@ -3490,7 +3490,7 @@
       <c r="F46" s="104" t="s">
         <v>256</v>
       </c>
-      <c r="G46" s="131">
+      <c r="G46" s="137">
         <v>90</v>
       </c>
       <c r="H46" s="104"/>
@@ -3500,9 +3500,9 @@
       <c r="J46" s="100"/>
     </row>
     <row r="47" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A47" s="119"/>
-      <c r="B47" s="119"/>
-      <c r="C47" s="130"/>
+      <c r="A47" s="132"/>
+      <c r="B47" s="132"/>
+      <c r="C47" s="136"/>
       <c r="D47" s="97">
         <v>2</v>
       </c>
@@ -3512,7 +3512,7 @@
       <c r="F47" s="104" t="s">
         <v>257</v>
       </c>
-      <c r="G47" s="131"/>
+      <c r="G47" s="137"/>
       <c r="H47" s="104"/>
       <c r="I47" s="94" t="s">
         <v>34</v>
@@ -3520,9 +3520,9 @@
       <c r="J47" s="100"/>
     </row>
     <row r="48" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A48" s="119"/>
-      <c r="B48" s="119"/>
-      <c r="C48" s="130"/>
+      <c r="A48" s="132"/>
+      <c r="B48" s="132"/>
+      <c r="C48" s="136"/>
       <c r="D48" s="97">
         <v>3</v>
       </c>
@@ -3532,7 +3532,7 @@
       <c r="F48" s="94" t="s">
         <v>188</v>
       </c>
-      <c r="G48" s="131"/>
+      <c r="G48" s="137"/>
       <c r="H48" s="104"/>
       <c r="I48" s="94" t="s">
         <v>34</v>
@@ -3540,9 +3540,9 @@
       <c r="J48" s="100"/>
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A49" s="119"/>
-      <c r="B49" s="119"/>
-      <c r="C49" s="130"/>
+      <c r="A49" s="132"/>
+      <c r="B49" s="132"/>
+      <c r="C49" s="136"/>
       <c r="D49" s="97">
         <v>4</v>
       </c>
@@ -3552,7 +3552,7 @@
       <c r="F49" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="G49" s="131"/>
+      <c r="G49" s="137"/>
       <c r="H49" s="104"/>
       <c r="I49" s="94" t="s">
         <v>34</v>
@@ -3560,9 +3560,9 @@
       <c r="J49" s="100"/>
     </row>
     <row r="50" spans="1:10" ht="19.25" customHeight="1">
-      <c r="A50" s="119"/>
-      <c r="B50" s="119"/>
-      <c r="C50" s="130"/>
+      <c r="A50" s="132"/>
+      <c r="B50" s="132"/>
+      <c r="C50" s="136"/>
       <c r="D50" s="97">
         <v>5</v>
       </c>
@@ -3572,7 +3572,7 @@
       <c r="F50" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="G50" s="131"/>
+      <c r="G50" s="137"/>
       <c r="H50" s="104" t="s">
         <v>201</v>
       </c>
@@ -3612,13 +3612,13 @@
       <c r="J51" s="100"/>
     </row>
     <row r="52" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A52" s="140" t="s">
+      <c r="A52" s="133" t="s">
         <v>83</v>
       </c>
-      <c r="B52" s="140" t="s">
+      <c r="B52" s="133" t="s">
         <v>208</v>
       </c>
-      <c r="C52" s="138" t="s">
+      <c r="C52" s="129" t="s">
         <v>211</v>
       </c>
       <c r="D52" s="93">
@@ -3630,7 +3630,7 @@
       <c r="F52" s="94" t="s">
         <v>262</v>
       </c>
-      <c r="G52" s="129">
+      <c r="G52" s="124">
         <v>60</v>
       </c>
       <c r="H52" s="94"/>
@@ -3642,9 +3642,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A53" s="140"/>
-      <c r="B53" s="140"/>
-      <c r="C53" s="138"/>
+      <c r="A53" s="133"/>
+      <c r="B53" s="133"/>
+      <c r="C53" s="129"/>
       <c r="D53" s="93">
         <v>3</v>
       </c>
@@ -3654,7 +3654,7 @@
       <c r="F53" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="G53" s="129"/>
+      <c r="G53" s="124"/>
       <c r="H53" s="94"/>
       <c r="I53" s="94" t="s">
         <v>34</v>
@@ -3662,9 +3662,9 @@
       <c r="J53" s="100"/>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A54" s="140"/>
-      <c r="B54" s="140"/>
-      <c r="C54" s="138"/>
+      <c r="A54" s="133"/>
+      <c r="B54" s="133"/>
+      <c r="C54" s="129"/>
       <c r="D54" s="93">
         <v>3</v>
       </c>
@@ -3674,7 +3674,7 @@
       <c r="F54" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="G54" s="129"/>
+      <c r="G54" s="124"/>
       <c r="H54" s="94"/>
       <c r="I54" s="94" t="s">
         <v>34</v>
@@ -3682,9 +3682,9 @@
       <c r="J54" s="100"/>
     </row>
     <row r="55" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A55" s="140"/>
-      <c r="B55" s="140"/>
-      <c r="C55" s="138"/>
+      <c r="A55" s="133"/>
+      <c r="B55" s="133"/>
+      <c r="C55" s="129"/>
       <c r="D55" s="93">
         <v>5</v>
       </c>
@@ -3694,7 +3694,7 @@
       <c r="F55" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="G55" s="129"/>
+      <c r="G55" s="124"/>
       <c r="H55" s="94"/>
       <c r="I55" s="94" t="s">
         <v>34</v>
@@ -3702,9 +3702,9 @@
       <c r="J55" s="100"/>
     </row>
     <row r="56" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A56" s="140"/>
-      <c r="B56" s="140"/>
-      <c r="C56" s="138"/>
+      <c r="A56" s="133"/>
+      <c r="B56" s="133"/>
+      <c r="C56" s="129"/>
       <c r="D56" s="93">
         <v>4</v>
       </c>
@@ -3714,7 +3714,7 @@
       <c r="F56" s="104" t="s">
         <v>263</v>
       </c>
-      <c r="G56" s="121"/>
+      <c r="G56" s="123"/>
       <c r="H56" s="104"/>
       <c r="I56" s="94" t="s">
         <v>34</v>
@@ -3722,25 +3722,25 @@
       <c r="J56" s="100"/>
     </row>
     <row r="57" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A57" s="134"/>
-      <c r="B57" s="121"/>
-      <c r="C57" s="121"/>
-      <c r="D57" s="121"/>
-      <c r="E57" s="121"/>
-      <c r="F57" s="121"/>
-      <c r="G57" s="121"/>
-      <c r="H57" s="121"/>
-      <c r="I57" s="121"/>
+      <c r="A57" s="131"/>
+      <c r="B57" s="123"/>
+      <c r="C57" s="123"/>
+      <c r="D57" s="123"/>
+      <c r="E57" s="123"/>
+      <c r="F57" s="123"/>
+      <c r="G57" s="123"/>
+      <c r="H57" s="123"/>
+      <c r="I57" s="123"/>
       <c r="J57" s="100"/>
     </row>
     <row r="58" spans="1:10" ht="21.4" customHeight="1">
-      <c r="A58" s="140" t="s">
+      <c r="A58" s="133" t="s">
         <v>83</v>
       </c>
-      <c r="B58" s="140" t="s">
+      <c r="B58" s="133" t="s">
         <v>212</v>
       </c>
-      <c r="C58" s="141" t="s">
+      <c r="C58" s="134" t="s">
         <v>213</v>
       </c>
       <c r="D58" s="99">
@@ -3752,7 +3752,7 @@
       <c r="F58" s="94" t="s">
         <v>190</v>
       </c>
-      <c r="G58" s="139">
+      <c r="G58" s="130">
         <v>90</v>
       </c>
       <c r="H58" s="98"/>
@@ -3764,9 +3764,9 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="21.4" customHeight="1">
-      <c r="A59" s="140"/>
-      <c r="B59" s="140"/>
-      <c r="C59" s="141"/>
+      <c r="A59" s="133"/>
+      <c r="B59" s="133"/>
+      <c r="C59" s="134"/>
       <c r="D59" s="99">
         <v>2</v>
       </c>
@@ -3776,7 +3776,7 @@
       <c r="F59" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="G59" s="139"/>
+      <c r="G59" s="130"/>
       <c r="H59" s="98"/>
       <c r="I59" s="94" t="s">
         <v>34</v>
@@ -3784,25 +3784,25 @@
       <c r="J59" s="100"/>
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A60" s="134"/>
-      <c r="B60" s="121"/>
-      <c r="C60" s="121"/>
-      <c r="D60" s="121"/>
-      <c r="E60" s="121"/>
-      <c r="F60" s="121"/>
-      <c r="G60" s="121"/>
-      <c r="H60" s="121"/>
-      <c r="I60" s="121"/>
+      <c r="A60" s="131"/>
+      <c r="B60" s="123"/>
+      <c r="C60" s="123"/>
+      <c r="D60" s="123"/>
+      <c r="E60" s="123"/>
+      <c r="F60" s="123"/>
+      <c r="G60" s="123"/>
+      <c r="H60" s="123"/>
+      <c r="I60" s="123"/>
       <c r="J60" s="100"/>
     </row>
     <row r="61" spans="1:10" ht="24" customHeight="1">
-      <c r="A61" s="120" t="s">
+      <c r="A61" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="B61" s="122" t="s">
+      <c r="B61" s="120" t="s">
         <v>218</v>
       </c>
-      <c r="C61" s="122" t="s">
+      <c r="C61" s="120" t="s">
         <v>216</v>
       </c>
       <c r="D61" s="99">
@@ -3814,7 +3814,7 @@
       <c r="F61" s="94" t="s">
         <v>262</v>
       </c>
-      <c r="G61" s="129">
+      <c r="G61" s="124">
         <v>60</v>
       </c>
       <c r="H61" s="94"/>
@@ -3826,9 +3826,9 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="23.25" customHeight="1">
-      <c r="A62" s="120"/>
-      <c r="B62" s="122"/>
-      <c r="C62" s="122"/>
+      <c r="A62" s="121"/>
+      <c r="B62" s="120"/>
+      <c r="C62" s="120"/>
       <c r="D62" s="99">
         <v>2</v>
       </c>
@@ -3838,7 +3838,7 @@
       <c r="F62" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="G62" s="129"/>
+      <c r="G62" s="124"/>
       <c r="H62" s="104" t="s">
         <v>221</v>
       </c>
@@ -3848,25 +3848,25 @@
       <c r="J62" s="100"/>
     </row>
     <row r="63" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A63" s="134"/>
-      <c r="B63" s="121"/>
-      <c r="C63" s="121"/>
-      <c r="D63" s="121"/>
-      <c r="E63" s="121"/>
-      <c r="F63" s="121"/>
-      <c r="G63" s="121"/>
-      <c r="H63" s="121"/>
-      <c r="I63" s="121"/>
+      <c r="A63" s="131"/>
+      <c r="B63" s="123"/>
+      <c r="C63" s="123"/>
+      <c r="D63" s="123"/>
+      <c r="E63" s="123"/>
+      <c r="F63" s="123"/>
+      <c r="G63" s="123"/>
+      <c r="H63" s="123"/>
+      <c r="I63" s="123"/>
       <c r="J63" s="100"/>
     </row>
     <row r="64" spans="1:10" ht="23.35" customHeight="1">
-      <c r="A64" s="120" t="s">
+      <c r="A64" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="B64" s="122" t="s">
+      <c r="B64" s="120" t="s">
         <v>215</v>
       </c>
-      <c r="C64" s="122" t="s">
+      <c r="C64" s="120" t="s">
         <v>219</v>
       </c>
       <c r="D64" s="93">
@@ -3878,7 +3878,7 @@
       <c r="F64" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="G64" s="129">
+      <c r="G64" s="124">
         <v>60</v>
       </c>
       <c r="H64" s="106" t="s">
@@ -3892,9 +3892,9 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="23.35" customHeight="1">
-      <c r="A65" s="120"/>
-      <c r="B65" s="122"/>
-      <c r="C65" s="122"/>
+      <c r="A65" s="121"/>
+      <c r="B65" s="120"/>
+      <c r="C65" s="120"/>
       <c r="D65" s="93">
         <v>2</v>
       </c>
@@ -3904,7 +3904,7 @@
       <c r="F65" s="94" t="s">
         <v>250</v>
       </c>
-      <c r="G65" s="129"/>
+      <c r="G65" s="124"/>
       <c r="H65" s="94"/>
       <c r="I65" s="94" t="s">
         <v>34</v>
@@ -3942,13 +3942,13 @@
       <c r="J66" s="100"/>
     </row>
     <row r="67" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A67" s="119" t="s">
+      <c r="A67" s="132" t="s">
         <v>99</v>
       </c>
-      <c r="B67" s="119" t="s">
+      <c r="B67" s="132" t="s">
         <v>223</v>
       </c>
-      <c r="C67" s="130" t="s">
+      <c r="C67" s="136" t="s">
         <v>209</v>
       </c>
       <c r="D67" s="97">
@@ -3960,7 +3960,7 @@
       <c r="F67" s="104" t="s">
         <v>256</v>
       </c>
-      <c r="G67" s="131">
+      <c r="G67" s="137">
         <v>90</v>
       </c>
       <c r="H67" s="104"/>
@@ -3970,9 +3970,9 @@
       <c r="J67" s="100"/>
     </row>
     <row r="68" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A68" s="119"/>
-      <c r="B68" s="119"/>
-      <c r="C68" s="130"/>
+      <c r="A68" s="132"/>
+      <c r="B68" s="132"/>
+      <c r="C68" s="136"/>
       <c r="D68" s="97">
         <v>2</v>
       </c>
@@ -3982,7 +3982,7 @@
       <c r="F68" s="104" t="s">
         <v>257</v>
       </c>
-      <c r="G68" s="131"/>
+      <c r="G68" s="137"/>
       <c r="H68" s="104"/>
       <c r="I68" s="94" t="s">
         <v>34</v>
@@ -3990,9 +3990,9 @@
       <c r="J68" s="100"/>
     </row>
     <row r="69" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A69" s="119"/>
-      <c r="B69" s="119"/>
-      <c r="C69" s="130"/>
+      <c r="A69" s="132"/>
+      <c r="B69" s="132"/>
+      <c r="C69" s="136"/>
       <c r="D69" s="97">
         <v>3</v>
       </c>
@@ -4002,7 +4002,7 @@
       <c r="F69" s="94" t="s">
         <v>188</v>
       </c>
-      <c r="G69" s="131"/>
+      <c r="G69" s="137"/>
       <c r="H69" s="104"/>
       <c r="I69" s="94" t="s">
         <v>34</v>
@@ -4010,9 +4010,9 @@
       <c r="J69" s="100"/>
     </row>
     <row r="70" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A70" s="119"/>
-      <c r="B70" s="119"/>
-      <c r="C70" s="130"/>
+      <c r="A70" s="132"/>
+      <c r="B70" s="132"/>
+      <c r="C70" s="136"/>
       <c r="D70" s="97">
         <v>4</v>
       </c>
@@ -4022,7 +4022,7 @@
       <c r="F70" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="G70" s="131"/>
+      <c r="G70" s="137"/>
       <c r="H70" s="104"/>
       <c r="I70" s="94" t="s">
         <v>34</v>
@@ -4030,9 +4030,9 @@
       <c r="J70" s="100"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A71" s="119"/>
-      <c r="B71" s="119"/>
-      <c r="C71" s="130"/>
+      <c r="A71" s="132"/>
+      <c r="B71" s="132"/>
+      <c r="C71" s="136"/>
       <c r="D71" s="97">
         <v>5</v>
       </c>
@@ -4042,7 +4042,7 @@
       <c r="F71" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="G71" s="131"/>
+      <c r="G71" s="137"/>
       <c r="H71" s="104" t="s">
         <v>201</v>
       </c>
@@ -4052,25 +4052,25 @@
       <c r="J71" s="100"/>
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A72" s="117"/>
-      <c r="B72" s="117"/>
-      <c r="C72" s="117"/>
-      <c r="D72" s="117"/>
-      <c r="E72" s="117"/>
-      <c r="F72" s="117"/>
-      <c r="G72" s="117"/>
-      <c r="H72" s="117"/>
-      <c r="I72" s="117"/>
+      <c r="A72" s="138"/>
+      <c r="B72" s="138"/>
+      <c r="C72" s="138"/>
+      <c r="D72" s="138"/>
+      <c r="E72" s="138"/>
+      <c r="F72" s="138"/>
+      <c r="G72" s="138"/>
+      <c r="H72" s="138"/>
+      <c r="I72" s="138"/>
       <c r="J72" s="100"/>
     </row>
     <row r="73" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A73" s="119" t="s">
+      <c r="A73" s="132" t="s">
         <v>224</v>
       </c>
-      <c r="B73" s="119" t="s">
+      <c r="B73" s="132" t="s">
         <v>225</v>
       </c>
-      <c r="C73" s="130" t="s">
+      <c r="C73" s="136" t="s">
         <v>226</v>
       </c>
       <c r="D73" s="93">
@@ -4082,7 +4082,7 @@
       <c r="F73" s="104" t="s">
         <v>255</v>
       </c>
-      <c r="G73" s="132">
+      <c r="G73" s="139">
         <v>60</v>
       </c>
       <c r="H73" s="104"/>
@@ -4090,9 +4090,9 @@
       <c r="J73" s="100"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A74" s="119"/>
-      <c r="B74" s="119"/>
-      <c r="C74" s="130"/>
+      <c r="A74" s="132"/>
+      <c r="B74" s="132"/>
+      <c r="C74" s="136"/>
       <c r="D74" s="93">
         <v>2</v>
       </c>
@@ -4102,7 +4102,7 @@
       <c r="F74" s="94" t="s">
         <v>253</v>
       </c>
-      <c r="G74" s="133"/>
+      <c r="G74" s="140"/>
       <c r="H74" s="104" t="s">
         <v>227</v>
       </c>
@@ -4110,25 +4110,25 @@
       <c r="J74" s="100"/>
     </row>
     <row r="75" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A75" s="117"/>
-      <c r="B75" s="117"/>
-      <c r="C75" s="117"/>
-      <c r="D75" s="117"/>
-      <c r="E75" s="117"/>
-      <c r="F75" s="117"/>
-      <c r="G75" s="117"/>
-      <c r="H75" s="117"/>
-      <c r="I75" s="117"/>
+      <c r="A75" s="138"/>
+      <c r="B75" s="138"/>
+      <c r="C75" s="138"/>
+      <c r="D75" s="138"/>
+      <c r="E75" s="138"/>
+      <c r="F75" s="138"/>
+      <c r="G75" s="138"/>
+      <c r="H75" s="138"/>
+      <c r="I75" s="138"/>
       <c r="J75" s="100"/>
     </row>
     <row r="76" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A76" s="119" t="s">
+      <c r="A76" s="132" t="s">
         <v>224</v>
       </c>
-      <c r="B76" s="119" t="s">
+      <c r="B76" s="132" t="s">
         <v>228</v>
       </c>
-      <c r="C76" s="118" t="s">
+      <c r="C76" s="141" t="s">
         <v>230</v>
       </c>
       <c r="D76" s="93">
@@ -4140,7 +4140,7 @@
       <c r="F76" s="104" t="s">
         <v>256</v>
       </c>
-      <c r="G76" s="129">
+      <c r="G76" s="124">
         <v>120</v>
       </c>
       <c r="H76" s="94" t="s">
@@ -4152,9 +4152,9 @@
       <c r="J76" s="100"/>
     </row>
     <row r="77" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A77" s="119"/>
-      <c r="B77" s="119"/>
-      <c r="C77" s="118"/>
+      <c r="A77" s="132"/>
+      <c r="B77" s="132"/>
+      <c r="C77" s="141"/>
       <c r="D77" s="93">
         <v>2</v>
       </c>
@@ -4164,7 +4164,7 @@
       <c r="F77" s="104" t="s">
         <v>255</v>
       </c>
-      <c r="G77" s="121"/>
+      <c r="G77" s="123"/>
       <c r="H77" s="94" t="s">
         <v>174</v>
       </c>
@@ -4174,9 +4174,9 @@
       <c r="J77" s="100"/>
     </row>
     <row r="78" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A78" s="119"/>
-      <c r="B78" s="119"/>
-      <c r="C78" s="118"/>
+      <c r="A78" s="132"/>
+      <c r="B78" s="132"/>
+      <c r="C78" s="141"/>
       <c r="D78" s="93">
         <v>3</v>
       </c>
@@ -4186,7 +4186,7 @@
       <c r="F78" s="104" t="s">
         <v>257</v>
       </c>
-      <c r="G78" s="121"/>
+      <c r="G78" s="123"/>
       <c r="H78" s="94" t="s">
         <v>177</v>
       </c>
@@ -4196,9 +4196,9 @@
       <c r="J78" s="100"/>
     </row>
     <row r="79" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A79" s="119"/>
-      <c r="B79" s="119"/>
-      <c r="C79" s="118"/>
+      <c r="A79" s="132"/>
+      <c r="B79" s="132"/>
+      <c r="C79" s="141"/>
       <c r="D79" s="93">
         <v>4</v>
       </c>
@@ -4208,7 +4208,7 @@
       <c r="F79" s="104" t="s">
         <v>258</v>
       </c>
-      <c r="G79" s="121"/>
+      <c r="G79" s="123"/>
       <c r="H79" s="94" t="s">
         <v>177</v>
       </c>
@@ -4218,9 +4218,9 @@
       <c r="J79" s="100"/>
     </row>
     <row r="80" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A80" s="119"/>
-      <c r="B80" s="119"/>
-      <c r="C80" s="118"/>
+      <c r="A80" s="132"/>
+      <c r="B80" s="132"/>
+      <c r="C80" s="141"/>
       <c r="D80" s="93">
         <v>5</v>
       </c>
@@ -4230,7 +4230,7 @@
       <c r="F80" s="94" t="s">
         <v>253</v>
       </c>
-      <c r="G80" s="121"/>
+      <c r="G80" s="123"/>
       <c r="H80" s="94"/>
       <c r="I80" s="94" t="s">
         <v>34</v>
@@ -4238,9 +4238,9 @@
       <c r="J80" s="100"/>
     </row>
     <row r="81" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A81" s="119"/>
-      <c r="B81" s="119"/>
-      <c r="C81" s="118"/>
+      <c r="A81" s="132"/>
+      <c r="B81" s="132"/>
+      <c r="C81" s="141"/>
       <c r="D81" s="93">
         <v>6</v>
       </c>
@@ -4250,7 +4250,7 @@
       <c r="F81" s="94" t="s">
         <v>188</v>
       </c>
-      <c r="G81" s="121"/>
+      <c r="G81" s="123"/>
       <c r="H81" s="94" t="s">
         <v>181</v>
       </c>
@@ -4260,9 +4260,9 @@
       <c r="J81" s="100"/>
     </row>
     <row r="82" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A82" s="119"/>
-      <c r="B82" s="119"/>
-      <c r="C82" s="118"/>
+      <c r="A82" s="132"/>
+      <c r="B82" s="132"/>
+      <c r="C82" s="141"/>
       <c r="D82" s="95">
         <v>7</v>
       </c>
@@ -4272,7 +4272,7 @@
       <c r="F82" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="G82" s="121"/>
+      <c r="G82" s="123"/>
       <c r="H82" s="94" t="s">
         <v>184</v>
       </c>
@@ -4282,25 +4282,25 @@
       <c r="J82" s="100"/>
     </row>
     <row r="83" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A83" s="117"/>
-      <c r="B83" s="117"/>
-      <c r="C83" s="117"/>
-      <c r="D83" s="117"/>
-      <c r="E83" s="117"/>
-      <c r="F83" s="117"/>
-      <c r="G83" s="117"/>
-      <c r="H83" s="117"/>
-      <c r="I83" s="117"/>
+      <c r="A83" s="138"/>
+      <c r="B83" s="138"/>
+      <c r="C83" s="138"/>
+      <c r="D83" s="138"/>
+      <c r="E83" s="138"/>
+      <c r="F83" s="138"/>
+      <c r="G83" s="138"/>
+      <c r="H83" s="138"/>
+      <c r="I83" s="138"/>
       <c r="J83" s="100"/>
     </row>
     <row r="84" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A84" s="119" t="s">
+      <c r="A84" s="132" t="s">
         <v>99</v>
       </c>
-      <c r="B84" s="119" t="s">
+      <c r="B84" s="132" t="s">
         <v>231</v>
       </c>
-      <c r="C84" s="118" t="s">
+      <c r="C84" s="141" t="s">
         <v>232</v>
       </c>
       <c r="D84" s="93">
@@ -4312,7 +4312,7 @@
       <c r="F84" s="104" t="s">
         <v>256</v>
       </c>
-      <c r="G84" s="123">
+      <c r="G84" s="142">
         <v>120</v>
       </c>
       <c r="H84" s="94"/>
@@ -4322,9 +4322,9 @@
       <c r="J84" s="100"/>
     </row>
     <row r="85" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A85" s="119"/>
-      <c r="B85" s="119"/>
-      <c r="C85" s="118"/>
+      <c r="A85" s="132"/>
+      <c r="B85" s="132"/>
+      <c r="C85" s="141"/>
       <c r="D85" s="93">
         <v>2</v>
       </c>
@@ -4334,7 +4334,7 @@
       <c r="F85" s="104" t="s">
         <v>260</v>
       </c>
-      <c r="G85" s="124"/>
+      <c r="G85" s="143"/>
       <c r="H85" s="94"/>
       <c r="I85" s="94" t="s">
         <v>34</v>
@@ -4342,9 +4342,9 @@
       <c r="J85" s="100"/>
     </row>
     <row r="86" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A86" s="119"/>
-      <c r="B86" s="119"/>
-      <c r="C86" s="118"/>
+      <c r="A86" s="132"/>
+      <c r="B86" s="132"/>
+      <c r="C86" s="141"/>
       <c r="D86" s="93">
         <v>3</v>
       </c>
@@ -4354,7 +4354,7 @@
       <c r="F86" s="104" t="s">
         <v>259</v>
       </c>
-      <c r="G86" s="125"/>
+      <c r="G86" s="144"/>
       <c r="H86" s="104" t="s">
         <v>235</v>
       </c>
@@ -4394,13 +4394,13 @@
       <c r="J87" s="100"/>
     </row>
     <row r="88" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A88" s="120" t="s">
+      <c r="A88" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="B88" s="122" t="s">
+      <c r="B88" s="120" t="s">
         <v>236</v>
       </c>
-      <c r="C88" s="122" t="s">
+      <c r="C88" s="120" t="s">
         <v>237</v>
       </c>
       <c r="D88" s="93">
@@ -4412,7 +4412,7 @@
       <c r="F88" s="94" t="s">
         <v>262</v>
       </c>
-      <c r="G88" s="126">
+      <c r="G88" s="145">
         <v>120</v>
       </c>
       <c r="H88" s="94"/>
@@ -4422,9 +4422,9 @@
       <c r="J88" s="100"/>
     </row>
     <row r="89" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A89" s="121"/>
-      <c r="B89" s="121"/>
-      <c r="C89" s="121"/>
+      <c r="A89" s="123"/>
+      <c r="B89" s="123"/>
+      <c r="C89" s="123"/>
       <c r="D89" s="93">
         <v>3</v>
       </c>
@@ -4434,7 +4434,7 @@
       <c r="F89" s="94" t="s">
         <v>248</v>
       </c>
-      <c r="G89" s="127"/>
+      <c r="G89" s="146"/>
       <c r="H89" s="94"/>
       <c r="I89" s="94" t="s">
         <v>34</v>
@@ -4442,9 +4442,9 @@
       <c r="J89" s="100"/>
     </row>
     <row r="90" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A90" s="121"/>
-      <c r="B90" s="121"/>
-      <c r="C90" s="121"/>
+      <c r="A90" s="123"/>
+      <c r="B90" s="123"/>
+      <c r="C90" s="123"/>
       <c r="D90" s="93">
         <v>3</v>
       </c>
@@ -4454,7 +4454,7 @@
       <c r="F90" s="94" t="s">
         <v>249</v>
       </c>
-      <c r="G90" s="127"/>
+      <c r="G90" s="146"/>
       <c r="H90" s="94"/>
       <c r="I90" s="94" t="s">
         <v>34</v>
@@ -4462,9 +4462,9 @@
       <c r="J90" s="100"/>
     </row>
     <row r="91" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A91" s="121"/>
-      <c r="B91" s="121"/>
-      <c r="C91" s="121"/>
+      <c r="A91" s="123"/>
+      <c r="B91" s="123"/>
+      <c r="C91" s="123"/>
       <c r="D91" s="93">
         <v>4</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="F91" s="94" t="s">
         <v>250</v>
       </c>
-      <c r="G91" s="127"/>
+      <c r="G91" s="146"/>
       <c r="H91" s="94" t="s">
         <v>158</v>
       </c>
@@ -4484,9 +4484,9 @@
       <c r="J91" s="100"/>
     </row>
     <row r="92" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A92" s="121"/>
-      <c r="B92" s="121"/>
-      <c r="C92" s="121"/>
+      <c r="A92" s="123"/>
+      <c r="B92" s="123"/>
+      <c r="C92" s="123"/>
       <c r="D92" s="93">
         <v>5</v>
       </c>
@@ -4496,7 +4496,7 @@
       <c r="F92" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="G92" s="127"/>
+      <c r="G92" s="146"/>
       <c r="H92" s="94"/>
       <c r="I92" s="94" t="s">
         <v>34</v>
@@ -4504,9 +4504,9 @@
       <c r="J92" s="100"/>
     </row>
     <row r="93" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A93" s="121"/>
-      <c r="B93" s="121"/>
-      <c r="C93" s="121"/>
+      <c r="A93" s="123"/>
+      <c r="B93" s="123"/>
+      <c r="C93" s="123"/>
       <c r="D93" s="93">
         <v>6</v>
       </c>
@@ -4516,15 +4516,15 @@
       <c r="F93" s="94" t="s">
         <v>188</v>
       </c>
-      <c r="G93" s="127"/>
+      <c r="G93" s="146"/>
       <c r="H93" s="109"/>
       <c r="I93" s="94"/>
       <c r="J93" s="100"/>
     </row>
     <row r="94" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A94" s="121"/>
-      <c r="B94" s="121"/>
-      <c r="C94" s="121"/>
+      <c r="A94" s="123"/>
+      <c r="B94" s="123"/>
+      <c r="C94" s="123"/>
       <c r="D94" s="95">
         <v>7</v>
       </c>
@@ -4534,7 +4534,7 @@
       <c r="F94" s="94" t="s">
         <v>189</v>
       </c>
-      <c r="G94" s="128"/>
+      <c r="G94" s="147"/>
       <c r="H94" s="109"/>
       <c r="I94" s="94"/>
       <c r="J94" s="100"/>
@@ -7081,6 +7081,87 @@
     </row>
   </sheetData>
   <mergeCells count="97">
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="C84:C86"/>
+    <mergeCell ref="B84:B86"/>
+    <mergeCell ref="A84:A86"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="B88:B94"/>
+    <mergeCell ref="C88:C94"/>
+    <mergeCell ref="G84:G86"/>
+    <mergeCell ref="G88:G94"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="G76:G82"/>
+    <mergeCell ref="C76:C82"/>
+    <mergeCell ref="B76:B82"/>
+    <mergeCell ref="A76:A82"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="G67:G71"/>
+    <mergeCell ref="B67:B71"/>
+    <mergeCell ref="C67:C71"/>
+    <mergeCell ref="G73:G74"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="G61:G62"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="G64:G65"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="G46:G50"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="G42:G44"/>
+    <mergeCell ref="B46:B50"/>
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="G52:G56"/>
+    <mergeCell ref="C52:C56"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="G4:G8"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="G17:G19"/>
     <mergeCell ref="G21:G22"/>
@@ -7097,87 +7178,6 @@
     <mergeCell ref="B38:B40"/>
     <mergeCell ref="C38:C40"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="G4:G8"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="G52:G56"/>
-    <mergeCell ref="C52:C56"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="A67:A71"/>
-    <mergeCell ref="A63:I63"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="G46:G50"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="G42:G44"/>
-    <mergeCell ref="B46:B50"/>
-    <mergeCell ref="A46:A50"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="G61:G62"/>
-    <mergeCell ref="A57:I57"/>
-    <mergeCell ref="A72:I72"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="C73:C74"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="G67:G71"/>
-    <mergeCell ref="B67:B71"/>
-    <mergeCell ref="C67:C71"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="G76:G82"/>
-    <mergeCell ref="C76:C82"/>
-    <mergeCell ref="B76:B82"/>
-    <mergeCell ref="A76:A82"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="C84:C86"/>
-    <mergeCell ref="B84:B86"/>
-    <mergeCell ref="A84:A86"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="B88:B94"/>
-    <mergeCell ref="C88:C94"/>
-    <mergeCell ref="G84:G86"/>
-    <mergeCell ref="G88:G94"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.64" bottom="0.08" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -7325,22 +7325,22 @@
       <c r="B5" s="104" t="s">
         <v>247</v>
       </c>
-      <c r="C5" s="169" t="s">
+      <c r="C5" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="D5" s="169" t="s">
+      <c r="D5" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="E5" s="169" t="s">
+      <c r="E5" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="F5" s="169" t="s">
+      <c r="F5" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="G5" s="169" t="s">
+      <c r="G5" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="H5" s="167" t="s">
+      <c r="H5" s="117" t="s">
         <v>239</v>
       </c>
       <c r="I5" s="110" t="s">
@@ -7412,22 +7412,22 @@
       <c r="B8" s="104" t="s">
         <v>250</v>
       </c>
-      <c r="C8" s="168" t="s">
+      <c r="C8" s="118" t="s">
         <v>239</v>
       </c>
-      <c r="D8" s="167" t="s">
+      <c r="D8" s="117" t="s">
         <v>239</v>
       </c>
-      <c r="E8" s="167" t="s">
+      <c r="E8" s="117" t="s">
         <v>239</v>
       </c>
-      <c r="F8" s="167" t="s">
+      <c r="F8" s="117" t="s">
         <v>239</v>
       </c>
       <c r="G8" s="112" t="s">
         <v>239</v>
       </c>
-      <c r="H8" s="167" t="s">
+      <c r="H8" s="117" t="s">
         <v>239</v>
       </c>
       <c r="I8" s="113" t="s">
@@ -8866,13 +8866,13 @@
       <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:10" ht="14.25">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="145" t="s">
+      <c r="B2" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="145" t="s">
+      <c r="C2" s="155" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="8">
@@ -8884,7 +8884,7 @@
       <c r="F2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="152">
+      <c r="G2" s="154">
         <v>191</v>
       </c>
       <c r="H2" s="9" t="s">
@@ -8894,9 +8894,9 @@
       <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10" ht="14.25">
-      <c r="A3" s="146"/>
-      <c r="B3" s="146"/>
-      <c r="C3" s="146"/>
+      <c r="A3" s="152"/>
+      <c r="B3" s="152"/>
+      <c r="C3" s="152"/>
       <c r="D3" s="8">
         <v>2</v>
       </c>
@@ -8906,7 +8906,7 @@
       <c r="F3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="146"/>
+      <c r="G3" s="152"/>
       <c r="H3" s="9" t="s">
         <v>23</v>
       </c>
@@ -8914,9 +8914,9 @@
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10" ht="14.25">
-      <c r="A4" s="146"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="146"/>
+      <c r="A4" s="152"/>
+      <c r="B4" s="152"/>
+      <c r="C4" s="152"/>
       <c r="D4" s="8">
         <v>3</v>
       </c>
@@ -8926,7 +8926,7 @@
       <c r="F4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="146"/>
+      <c r="G4" s="152"/>
       <c r="H4" s="9" t="s">
         <v>23</v>
       </c>
@@ -8934,9 +8934,9 @@
       <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10" ht="14.25">
-      <c r="A5" s="146"/>
-      <c r="B5" s="146"/>
-      <c r="C5" s="146"/>
+      <c r="A5" s="152"/>
+      <c r="B5" s="152"/>
+      <c r="C5" s="152"/>
       <c r="D5" s="8">
         <v>5</v>
       </c>
@@ -8946,7 +8946,7 @@
       <c r="F5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="146"/>
+      <c r="G5" s="152"/>
       <c r="H5" s="9" t="s">
         <v>23</v>
       </c>
@@ -8954,9 +8954,9 @@
       <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10" ht="14.25">
-      <c r="A6" s="147"/>
-      <c r="B6" s="147"/>
-      <c r="C6" s="147"/>
+      <c r="A6" s="153"/>
+      <c r="B6" s="153"/>
+      <c r="C6" s="153"/>
       <c r="D6" s="8">
         <v>6</v>
       </c>
@@ -8966,7 +8966,7 @@
       <c r="F6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="147"/>
+      <c r="G6" s="153"/>
       <c r="H6" s="9" t="s">
         <v>23</v>
       </c>
@@ -8974,7 +8974,7 @@
       <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10" ht="14.25">
-      <c r="A7" s="154"/>
+      <c r="A7" s="156"/>
       <c r="B7" s="149"/>
       <c r="C7" s="149"/>
       <c r="D7" s="149"/>
@@ -8986,13 +8986,13 @@
       <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10" ht="14.25">
-      <c r="A8" s="145" t="s">
+      <c r="A8" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="145" t="s">
+      <c r="B8" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="145" t="s">
+      <c r="C8" s="155" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="8">
@@ -9004,7 +9004,7 @@
       <c r="F8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="152">
+      <c r="G8" s="154">
         <v>140</v>
       </c>
       <c r="H8" s="9" t="s">
@@ -9014,9 +9014,9 @@
       <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10" ht="14.25">
-      <c r="A9" s="146"/>
-      <c r="B9" s="146"/>
-      <c r="C9" s="146"/>
+      <c r="A9" s="152"/>
+      <c r="B9" s="152"/>
+      <c r="C9" s="152"/>
       <c r="D9" s="8">
         <v>2</v>
       </c>
@@ -9026,7 +9026,7 @@
       <c r="F9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="146"/>
+      <c r="G9" s="152"/>
       <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
@@ -9034,9 +9034,9 @@
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10" ht="14.25">
-      <c r="A10" s="146"/>
-      <c r="B10" s="146"/>
-      <c r="C10" s="146"/>
+      <c r="A10" s="152"/>
+      <c r="B10" s="152"/>
+      <c r="C10" s="152"/>
       <c r="D10" s="8">
         <v>3</v>
       </c>
@@ -9046,7 +9046,7 @@
       <c r="F10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="146"/>
+      <c r="G10" s="152"/>
       <c r="H10" s="9" t="s">
         <v>23</v>
       </c>
@@ -9054,9 +9054,9 @@
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="14.25">
-      <c r="A11" s="146"/>
-      <c r="B11" s="146"/>
-      <c r="C11" s="146"/>
+      <c r="A11" s="152"/>
+      <c r="B11" s="152"/>
+      <c r="C11" s="152"/>
       <c r="D11" s="8">
         <v>5</v>
       </c>
@@ -9066,7 +9066,7 @@
       <c r="F11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="146"/>
+      <c r="G11" s="152"/>
       <c r="H11" s="9" t="s">
         <v>23</v>
       </c>
@@ -9074,9 +9074,9 @@
       <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="14.25">
-      <c r="A12" s="147"/>
-      <c r="B12" s="147"/>
-      <c r="C12" s="147"/>
+      <c r="A12" s="153"/>
+      <c r="B12" s="153"/>
+      <c r="C12" s="153"/>
       <c r="D12" s="8">
         <v>6</v>
       </c>
@@ -9086,7 +9086,7 @@
       <c r="F12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="147"/>
+      <c r="G12" s="153"/>
       <c r="H12" s="9" t="s">
         <v>23</v>
       </c>
@@ -9094,7 +9094,7 @@
       <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="14.25">
-      <c r="A13" s="154"/>
+      <c r="A13" s="156"/>
       <c r="B13" s="149"/>
       <c r="C13" s="149"/>
       <c r="D13" s="149"/>
@@ -9106,13 +9106,13 @@
       <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="14.25">
-      <c r="A14" s="145" t="s">
+      <c r="A14" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="145" t="s">
+      <c r="B14" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="145" t="s">
+      <c r="C14" s="155" t="s">
         <v>41</v>
       </c>
       <c r="D14" s="8">
@@ -9134,9 +9134,9 @@
       <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="14.25">
-      <c r="A15" s="146"/>
-      <c r="B15" s="146"/>
-      <c r="C15" s="146"/>
+      <c r="A15" s="152"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="152"/>
       <c r="D15" s="8">
         <v>2</v>
       </c>
@@ -9146,7 +9146,7 @@
       <c r="F15" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="146"/>
+      <c r="G15" s="152"/>
       <c r="H15" s="9" t="s">
         <v>23</v>
       </c>
@@ -9154,9 +9154,9 @@
       <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:10" ht="14.25">
-      <c r="A16" s="146"/>
-      <c r="B16" s="146"/>
-      <c r="C16" s="146"/>
+      <c r="A16" s="152"/>
+      <c r="B16" s="152"/>
+      <c r="C16" s="152"/>
       <c r="D16" s="8">
         <v>7</v>
       </c>
@@ -9166,7 +9166,7 @@
       <c r="F16" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="146"/>
+      <c r="G16" s="152"/>
       <c r="H16" s="9" t="s">
         <v>23</v>
       </c>
@@ -9176,9 +9176,9 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="14.25">
-      <c r="A17" s="146"/>
-      <c r="B17" s="146"/>
-      <c r="C17" s="146"/>
+      <c r="A17" s="152"/>
+      <c r="B17" s="152"/>
+      <c r="C17" s="152"/>
       <c r="D17" s="8">
         <v>8</v>
       </c>
@@ -9188,7 +9188,7 @@
       <c r="F17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="146"/>
+      <c r="G17" s="152"/>
       <c r="H17" s="9" t="s">
         <v>23</v>
       </c>
@@ -9196,9 +9196,9 @@
       <c r="J17" s="7"/>
     </row>
     <row r="18" spans="1:10" ht="14.25">
-      <c r="A18" s="147"/>
-      <c r="B18" s="147"/>
-      <c r="C18" s="147"/>
+      <c r="A18" s="153"/>
+      <c r="B18" s="153"/>
+      <c r="C18" s="153"/>
       <c r="D18" s="8">
         <v>9</v>
       </c>
@@ -9208,7 +9208,7 @@
       <c r="F18" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="147"/>
+      <c r="G18" s="153"/>
       <c r="H18" s="9" t="s">
         <v>23</v>
       </c>
@@ -9216,7 +9216,7 @@
       <c r="J18" s="7"/>
     </row>
     <row r="19" spans="1:10" ht="14.25">
-      <c r="A19" s="154"/>
+      <c r="A19" s="156"/>
       <c r="B19" s="149"/>
       <c r="C19" s="149"/>
       <c r="D19" s="149"/>
@@ -9228,13 +9228,13 @@
       <c r="J19" s="7"/>
     </row>
     <row r="20" spans="1:10" ht="14.25">
-      <c r="A20" s="145" t="s">
+      <c r="A20" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="145" t="s">
+      <c r="B20" s="155" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="145" t="s">
+      <c r="C20" s="155" t="s">
         <v>46</v>
       </c>
       <c r="D20" s="8">
@@ -9256,9 +9256,9 @@
       <c r="J20" s="7"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A21" s="146"/>
-      <c r="B21" s="146"/>
-      <c r="C21" s="146"/>
+      <c r="A21" s="152"/>
+      <c r="B21" s="152"/>
+      <c r="C21" s="152"/>
       <c r="D21" s="8">
         <v>2</v>
       </c>
@@ -9268,7 +9268,7 @@
       <c r="F21" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="146"/>
+      <c r="G21" s="152"/>
       <c r="H21" s="9" t="s">
         <v>23</v>
       </c>
@@ -9276,9 +9276,9 @@
       <c r="J21" s="7"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A22" s="146"/>
-      <c r="B22" s="146"/>
-      <c r="C22" s="146"/>
+      <c r="A22" s="152"/>
+      <c r="B22" s="152"/>
+      <c r="C22" s="152"/>
       <c r="D22" s="8">
         <v>4</v>
       </c>
@@ -9288,7 +9288,7 @@
       <c r="F22" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="146"/>
+      <c r="G22" s="152"/>
       <c r="H22" s="9" t="s">
         <v>23</v>
       </c>
@@ -9296,9 +9296,9 @@
       <c r="J22" s="7"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A23" s="146"/>
-      <c r="B23" s="146"/>
-      <c r="C23" s="146"/>
+      <c r="A23" s="152"/>
+      <c r="B23" s="152"/>
+      <c r="C23" s="152"/>
       <c r="D23" s="8">
         <v>5</v>
       </c>
@@ -9308,7 +9308,7 @@
       <c r="F23" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="146"/>
+      <c r="G23" s="152"/>
       <c r="H23" s="9" t="s">
         <v>23</v>
       </c>
@@ -9316,9 +9316,9 @@
       <c r="J23" s="7"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A24" s="147"/>
-      <c r="B24" s="147"/>
-      <c r="C24" s="147"/>
+      <c r="A24" s="153"/>
+      <c r="B24" s="153"/>
+      <c r="C24" s="153"/>
       <c r="D24" s="8">
         <v>6</v>
       </c>
@@ -9328,7 +9328,7 @@
       <c r="F24" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="147"/>
+      <c r="G24" s="153"/>
       <c r="H24" s="9" t="s">
         <v>23</v>
       </c>
@@ -9336,7 +9336,7 @@
       <c r="J24" s="7"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A25" s="154"/>
+      <c r="A25" s="156"/>
       <c r="B25" s="149"/>
       <c r="C25" s="149"/>
       <c r="D25" s="149"/>
@@ -9348,13 +9348,13 @@
       <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A26" s="145" t="s">
+      <c r="A26" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="145" t="s">
+      <c r="B26" s="155" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="145" t="s">
+      <c r="C26" s="155" t="s">
         <v>51</v>
       </c>
       <c r="D26" s="8">
@@ -9376,9 +9376,9 @@
       <c r="J26" s="7"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A27" s="146"/>
-      <c r="B27" s="146"/>
-      <c r="C27" s="146"/>
+      <c r="A27" s="152"/>
+      <c r="B27" s="152"/>
+      <c r="C27" s="152"/>
       <c r="D27" s="8">
         <v>2</v>
       </c>
@@ -9388,7 +9388,7 @@
       <c r="F27" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G27" s="146"/>
+      <c r="G27" s="152"/>
       <c r="H27" s="9" t="s">
         <v>23</v>
       </c>
@@ -9396,9 +9396,9 @@
       <c r="J27" s="7"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A28" s="146"/>
-      <c r="B28" s="146"/>
-      <c r="C28" s="146"/>
+      <c r="A28" s="152"/>
+      <c r="B28" s="152"/>
+      <c r="C28" s="152"/>
       <c r="D28" s="8">
         <v>4</v>
       </c>
@@ -9408,7 +9408,7 @@
       <c r="F28" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G28" s="146"/>
+      <c r="G28" s="152"/>
       <c r="H28" s="9" t="s">
         <v>23</v>
       </c>
@@ -9416,9 +9416,9 @@
       <c r="J28" s="7"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A29" s="146"/>
-      <c r="B29" s="146"/>
-      <c r="C29" s="146"/>
+      <c r="A29" s="152"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="152"/>
       <c r="D29" s="8">
         <v>5</v>
       </c>
@@ -9428,7 +9428,7 @@
       <c r="F29" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G29" s="146"/>
+      <c r="G29" s="152"/>
       <c r="H29" s="9" t="s">
         <v>23</v>
       </c>
@@ -9436,9 +9436,9 @@
       <c r="J29" s="7"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A30" s="147"/>
-      <c r="B30" s="147"/>
-      <c r="C30" s="147"/>
+      <c r="A30" s="153"/>
+      <c r="B30" s="153"/>
+      <c r="C30" s="153"/>
       <c r="D30" s="8">
         <v>6</v>
       </c>
@@ -9448,7 +9448,7 @@
       <c r="F30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G30" s="147"/>
+      <c r="G30" s="153"/>
       <c r="H30" s="9" t="s">
         <v>23</v>
       </c>
@@ -9456,7 +9456,7 @@
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A31" s="154"/>
+      <c r="A31" s="156"/>
       <c r="B31" s="149"/>
       <c r="C31" s="149"/>
       <c r="D31" s="149"/>
@@ -9468,13 +9468,13 @@
       <c r="J31" s="7"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A32" s="145" t="s">
+      <c r="A32" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="145" t="s">
+      <c r="B32" s="155" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="145" t="s">
+      <c r="C32" s="155" t="s">
         <v>55</v>
       </c>
       <c r="D32" s="8">
@@ -9496,9 +9496,9 @@
       <c r="J32" s="7"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A33" s="146"/>
-      <c r="B33" s="146"/>
-      <c r="C33" s="146"/>
+      <c r="A33" s="152"/>
+      <c r="B33" s="152"/>
+      <c r="C33" s="152"/>
       <c r="D33" s="8">
         <v>2</v>
       </c>
@@ -9508,7 +9508,7 @@
       <c r="F33" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G33" s="146"/>
+      <c r="G33" s="152"/>
       <c r="H33" s="9" t="s">
         <v>23</v>
       </c>
@@ -9516,9 +9516,9 @@
       <c r="J33" s="7"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A34" s="146"/>
-      <c r="B34" s="146"/>
-      <c r="C34" s="146"/>
+      <c r="A34" s="152"/>
+      <c r="B34" s="152"/>
+      <c r="C34" s="152"/>
       <c r="D34" s="8">
         <v>5</v>
       </c>
@@ -9528,7 +9528,7 @@
       <c r="F34" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G34" s="146"/>
+      <c r="G34" s="152"/>
       <c r="H34" s="9" t="s">
         <v>23</v>
       </c>
@@ -9538,9 +9538,9 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A35" s="146"/>
-      <c r="B35" s="146"/>
-      <c r="C35" s="146"/>
+      <c r="A35" s="152"/>
+      <c r="B35" s="152"/>
+      <c r="C35" s="152"/>
       <c r="D35" s="8">
         <v>6</v>
       </c>
@@ -9550,7 +9550,7 @@
       <c r="F35" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G35" s="146"/>
+      <c r="G35" s="152"/>
       <c r="H35" s="9" t="s">
         <v>23</v>
       </c>
@@ -9558,9 +9558,9 @@
       <c r="J35" s="7"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A36" s="147"/>
-      <c r="B36" s="147"/>
-      <c r="C36" s="147"/>
+      <c r="A36" s="153"/>
+      <c r="B36" s="153"/>
+      <c r="C36" s="153"/>
       <c r="D36" s="8">
         <v>7</v>
       </c>
@@ -9570,7 +9570,7 @@
       <c r="F36" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G36" s="147"/>
+      <c r="G36" s="153"/>
       <c r="H36" s="9" t="s">
         <v>23</v>
       </c>
@@ -9608,13 +9608,13 @@
       <c r="J37" s="7"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A38" s="145" t="s">
+      <c r="A38" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="B38" s="145" t="s">
+      <c r="B38" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="145" t="s">
+      <c r="C38" s="155" t="s">
         <v>62</v>
       </c>
       <c r="D38" s="8">
@@ -9636,9 +9636,9 @@
       <c r="J38" s="7"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A39" s="146"/>
-      <c r="B39" s="146"/>
-      <c r="C39" s="146"/>
+      <c r="A39" s="152"/>
+      <c r="B39" s="152"/>
+      <c r="C39" s="152"/>
       <c r="D39" s="8">
         <v>2</v>
       </c>
@@ -9648,7 +9648,7 @@
       <c r="F39" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G39" s="146"/>
+      <c r="G39" s="152"/>
       <c r="H39" s="9" t="s">
         <v>23</v>
       </c>
@@ -9656,9 +9656,9 @@
       <c r="J39" s="7"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A40" s="146"/>
-      <c r="B40" s="146"/>
-      <c r="C40" s="146"/>
+      <c r="A40" s="152"/>
+      <c r="B40" s="152"/>
+      <c r="C40" s="152"/>
       <c r="D40" s="8">
         <v>8</v>
       </c>
@@ -9668,7 +9668,7 @@
       <c r="F40" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G40" s="146"/>
+      <c r="G40" s="152"/>
       <c r="H40" s="9" t="s">
         <v>23</v>
       </c>
@@ -9676,9 +9676,9 @@
       <c r="J40" s="7"/>
     </row>
     <row r="41" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A41" s="146"/>
-      <c r="B41" s="146"/>
-      <c r="C41" s="146"/>
+      <c r="A41" s="152"/>
+      <c r="B41" s="152"/>
+      <c r="C41" s="152"/>
       <c r="D41" s="8">
         <v>9</v>
       </c>
@@ -9688,7 +9688,7 @@
       <c r="F41" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G41" s="146"/>
+      <c r="G41" s="152"/>
       <c r="H41" s="9" t="s">
         <v>23</v>
       </c>
@@ -9696,9 +9696,9 @@
       <c r="J41" s="7"/>
     </row>
     <row r="42" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A42" s="147"/>
-      <c r="B42" s="147"/>
-      <c r="C42" s="147"/>
+      <c r="A42" s="153"/>
+      <c r="B42" s="153"/>
+      <c r="C42" s="153"/>
       <c r="D42" s="8">
         <v>10</v>
       </c>
@@ -9708,7 +9708,7 @@
       <c r="F42" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G42" s="147"/>
+      <c r="G42" s="153"/>
       <c r="H42" s="9" t="s">
         <v>23</v>
       </c>
@@ -9728,13 +9728,13 @@
       <c r="J43" s="7"/>
     </row>
     <row r="44" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A44" s="145" t="s">
+      <c r="A44" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="B44" s="145" t="s">
+      <c r="B44" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="C44" s="145" t="s">
+      <c r="C44" s="155" t="s">
         <v>66</v>
       </c>
       <c r="D44" s="8">
@@ -9756,9 +9756,9 @@
       <c r="J44" s="7"/>
     </row>
     <row r="45" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A45" s="146"/>
-      <c r="B45" s="146"/>
-      <c r="C45" s="146"/>
+      <c r="A45" s="152"/>
+      <c r="B45" s="152"/>
+      <c r="C45" s="152"/>
       <c r="D45" s="8">
         <v>2</v>
       </c>
@@ -9768,7 +9768,7 @@
       <c r="F45" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G45" s="146"/>
+      <c r="G45" s="152"/>
       <c r="H45" s="9" t="s">
         <v>23</v>
       </c>
@@ -9776,9 +9776,9 @@
       <c r="J45" s="7"/>
     </row>
     <row r="46" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A46" s="146"/>
-      <c r="B46" s="146"/>
-      <c r="C46" s="146"/>
+      <c r="A46" s="152"/>
+      <c r="B46" s="152"/>
+      <c r="C46" s="152"/>
       <c r="D46" s="8">
         <v>3</v>
       </c>
@@ -9788,7 +9788,7 @@
       <c r="F46" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G46" s="146"/>
+      <c r="G46" s="152"/>
       <c r="H46" s="9" t="s">
         <v>23</v>
       </c>
@@ -9796,9 +9796,9 @@
       <c r="J46" s="7"/>
     </row>
     <row r="47" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A47" s="146"/>
-      <c r="B47" s="146"/>
-      <c r="C47" s="146"/>
+      <c r="A47" s="152"/>
+      <c r="B47" s="152"/>
+      <c r="C47" s="152"/>
       <c r="D47" s="8">
         <v>4</v>
       </c>
@@ -9808,7 +9808,7 @@
       <c r="F47" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G47" s="146"/>
+      <c r="G47" s="152"/>
       <c r="H47" s="9" t="s">
         <v>23</v>
       </c>
@@ -9816,9 +9816,9 @@
       <c r="J47" s="7"/>
     </row>
     <row r="48" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A48" s="147"/>
-      <c r="B48" s="147"/>
-      <c r="C48" s="147"/>
+      <c r="A48" s="153"/>
+      <c r="B48" s="153"/>
+      <c r="C48" s="153"/>
       <c r="D48" s="8">
         <v>10</v>
       </c>
@@ -9828,7 +9828,7 @@
       <c r="F48" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G48" s="147"/>
+      <c r="G48" s="153"/>
       <c r="H48" s="9" t="s">
         <v>23</v>
       </c>
@@ -9848,13 +9848,13 @@
       <c r="J49" s="7"/>
     </row>
     <row r="50" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A50" s="145" t="s">
+      <c r="A50" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="B50" s="145" t="s">
+      <c r="B50" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="145" t="s">
+      <c r="C50" s="155" t="s">
         <v>70</v>
       </c>
       <c r="D50" s="8">
@@ -9876,9 +9876,9 @@
       <c r="J50" s="7"/>
     </row>
     <row r="51" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A51" s="146"/>
-      <c r="B51" s="146"/>
-      <c r="C51" s="146"/>
+      <c r="A51" s="152"/>
+      <c r="B51" s="152"/>
+      <c r="C51" s="152"/>
       <c r="D51" s="8">
         <v>2</v>
       </c>
@@ -9888,7 +9888,7 @@
       <c r="F51" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G51" s="146"/>
+      <c r="G51" s="152"/>
       <c r="H51" s="9" t="s">
         <v>23</v>
       </c>
@@ -9896,9 +9896,9 @@
       <c r="J51" s="7"/>
     </row>
     <row r="52" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A52" s="146"/>
-      <c r="B52" s="146"/>
-      <c r="C52" s="146"/>
+      <c r="A52" s="152"/>
+      <c r="B52" s="152"/>
+      <c r="C52" s="152"/>
       <c r="D52" s="8">
         <v>3</v>
       </c>
@@ -9908,7 +9908,7 @@
       <c r="F52" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G52" s="146"/>
+      <c r="G52" s="152"/>
       <c r="H52" s="9" t="s">
         <v>23</v>
       </c>
@@ -9916,9 +9916,9 @@
       <c r="J52" s="7"/>
     </row>
     <row r="53" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A53" s="146"/>
-      <c r="B53" s="146"/>
-      <c r="C53" s="146"/>
+      <c r="A53" s="152"/>
+      <c r="B53" s="152"/>
+      <c r="C53" s="152"/>
       <c r="D53" s="8">
         <v>4</v>
       </c>
@@ -9928,7 +9928,7 @@
       <c r="F53" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G53" s="146"/>
+      <c r="G53" s="152"/>
       <c r="H53" s="9" t="s">
         <v>23</v>
       </c>
@@ -9936,9 +9936,9 @@
       <c r="J53" s="7"/>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A54" s="147"/>
-      <c r="B54" s="147"/>
-      <c r="C54" s="147"/>
+      <c r="A54" s="153"/>
+      <c r="B54" s="153"/>
+      <c r="C54" s="153"/>
       <c r="D54" s="8">
         <v>7</v>
       </c>
@@ -9948,7 +9948,7 @@
       <c r="F54" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G54" s="147"/>
+      <c r="G54" s="153"/>
       <c r="H54" s="9" t="s">
         <v>23</v>
       </c>
@@ -9968,13 +9968,13 @@
       <c r="J55" s="7"/>
     </row>
     <row r="56" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A56" s="145" t="s">
+      <c r="A56" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="145" t="s">
+      <c r="B56" s="155" t="s">
         <v>45</v>
       </c>
-      <c r="C56" s="145" t="s">
+      <c r="C56" s="155" t="s">
         <v>74</v>
       </c>
       <c r="D56" s="8">
@@ -9986,7 +9986,7 @@
       <c r="F56" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G56" s="152">
+      <c r="G56" s="154">
         <v>49</v>
       </c>
       <c r="H56" s="9" t="s">
@@ -9996,9 +9996,9 @@
       <c r="J56" s="7"/>
     </row>
     <row r="57" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A57" s="146"/>
-      <c r="B57" s="146"/>
-      <c r="C57" s="146"/>
+      <c r="A57" s="152"/>
+      <c r="B57" s="152"/>
+      <c r="C57" s="152"/>
       <c r="D57" s="8">
         <v>2</v>
       </c>
@@ -10008,7 +10008,7 @@
       <c r="F57" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G57" s="146"/>
+      <c r="G57" s="152"/>
       <c r="H57" s="9" t="s">
         <v>23</v>
       </c>
@@ -10016,9 +10016,9 @@
       <c r="J57" s="7"/>
     </row>
     <row r="58" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A58" s="146"/>
-      <c r="B58" s="146"/>
-      <c r="C58" s="146"/>
+      <c r="A58" s="152"/>
+      <c r="B58" s="152"/>
+      <c r="C58" s="152"/>
       <c r="D58" s="8">
         <v>3</v>
       </c>
@@ -10028,7 +10028,7 @@
       <c r="F58" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G58" s="146"/>
+      <c r="G58" s="152"/>
       <c r="H58" s="9" t="s">
         <v>23</v>
       </c>
@@ -10036,9 +10036,9 @@
       <c r="J58" s="7"/>
     </row>
     <row r="59" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A59" s="146"/>
-      <c r="B59" s="146"/>
-      <c r="C59" s="146"/>
+      <c r="A59" s="152"/>
+      <c r="B59" s="152"/>
+      <c r="C59" s="152"/>
       <c r="D59" s="8">
         <v>4</v>
       </c>
@@ -10048,7 +10048,7 @@
       <c r="F59" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G59" s="146"/>
+      <c r="G59" s="152"/>
       <c r="H59" s="9" t="s">
         <v>23</v>
       </c>
@@ -10056,9 +10056,9 @@
       <c r="J59" s="7"/>
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A60" s="147"/>
-      <c r="B60" s="147"/>
-      <c r="C60" s="147"/>
+      <c r="A60" s="153"/>
+      <c r="B60" s="153"/>
+      <c r="C60" s="153"/>
       <c r="D60" s="8">
         <v>7</v>
       </c>
@@ -10068,7 +10068,7 @@
       <c r="F60" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G60" s="147"/>
+      <c r="G60" s="153"/>
       <c r="H60" s="9" t="s">
         <v>23</v>
       </c>
@@ -10106,13 +10106,13 @@
       <c r="J61" s="7"/>
     </row>
     <row r="62" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A62" s="145" t="s">
+      <c r="A62" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="B62" s="145" t="s">
+      <c r="B62" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C62" s="145" t="s">
+      <c r="C62" s="155" t="s">
         <v>79</v>
       </c>
       <c r="D62" s="8">
@@ -10124,7 +10124,7 @@
       <c r="F62" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G62" s="152">
+      <c r="G62" s="154">
         <v>190</v>
       </c>
       <c r="H62" s="9" t="s">
@@ -10134,9 +10134,9 @@
       <c r="J62" s="7"/>
     </row>
     <row r="63" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A63" s="146"/>
-      <c r="B63" s="146"/>
-      <c r="C63" s="146"/>
+      <c r="A63" s="152"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
       <c r="D63" s="8">
         <v>2</v>
       </c>
@@ -10146,7 +10146,7 @@
       <c r="F63" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G63" s="146"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="9" t="s">
         <v>23</v>
       </c>
@@ -10154,9 +10154,9 @@
       <c r="J63" s="7"/>
     </row>
     <row r="64" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A64" s="146"/>
-      <c r="B64" s="146"/>
-      <c r="C64" s="146"/>
+      <c r="A64" s="152"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
       <c r="D64" s="8">
         <v>3</v>
       </c>
@@ -10166,7 +10166,7 @@
       <c r="F64" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G64" s="146"/>
+      <c r="G64" s="152"/>
       <c r="H64" s="9" t="s">
         <v>23</v>
       </c>
@@ -10174,9 +10174,9 @@
       <c r="J64" s="7"/>
     </row>
     <row r="65" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A65" s="146"/>
-      <c r="B65" s="146"/>
-      <c r="C65" s="146"/>
+      <c r="A65" s="152"/>
+      <c r="B65" s="152"/>
+      <c r="C65" s="152"/>
       <c r="D65" s="8">
         <v>4</v>
       </c>
@@ -10186,7 +10186,7 @@
       <c r="F65" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G65" s="146"/>
+      <c r="G65" s="152"/>
       <c r="H65" s="9" t="s">
         <v>23</v>
       </c>
@@ -10194,9 +10194,9 @@
       <c r="J65" s="7"/>
     </row>
     <row r="66" spans="1:10" ht="23.25" customHeight="1">
-      <c r="A66" s="147"/>
-      <c r="B66" s="147"/>
-      <c r="C66" s="147"/>
+      <c r="A66" s="153"/>
+      <c r="B66" s="153"/>
+      <c r="C66" s="153"/>
       <c r="D66" s="8">
         <v>7</v>
       </c>
@@ -10206,7 +10206,7 @@
       <c r="F66" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G66" s="147"/>
+      <c r="G66" s="153"/>
       <c r="H66" s="9" t="s">
         <v>23</v>
       </c>
@@ -10244,13 +10244,13 @@
       <c r="J67" s="7"/>
     </row>
     <row r="68" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A68" s="145" t="s">
+      <c r="A68" s="155" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="145" t="s">
+      <c r="B68" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C68" s="145" t="s">
+      <c r="C68" s="155" t="s">
         <v>84</v>
       </c>
       <c r="D68" s="8">
@@ -10262,7 +10262,7 @@
       <c r="F68" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G68" s="152">
+      <c r="G68" s="154">
         <v>59</v>
       </c>
       <c r="H68" s="9" t="s">
@@ -10272,9 +10272,9 @@
       <c r="J68" s="7"/>
     </row>
     <row r="69" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A69" s="146"/>
-      <c r="B69" s="146"/>
-      <c r="C69" s="146"/>
+      <c r="A69" s="152"/>
+      <c r="B69" s="152"/>
+      <c r="C69" s="152"/>
       <c r="D69" s="8">
         <v>2</v>
       </c>
@@ -10284,7 +10284,7 @@
       <c r="F69" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G69" s="146"/>
+      <c r="G69" s="152"/>
       <c r="H69" s="9" t="s">
         <v>23</v>
       </c>
@@ -10292,9 +10292,9 @@
       <c r="J69" s="7"/>
     </row>
     <row r="70" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A70" s="146"/>
-      <c r="B70" s="146"/>
-      <c r="C70" s="146"/>
+      <c r="A70" s="152"/>
+      <c r="B70" s="152"/>
+      <c r="C70" s="152"/>
       <c r="D70" s="8">
         <v>3</v>
       </c>
@@ -10304,7 +10304,7 @@
       <c r="F70" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="G70" s="146"/>
+      <c r="G70" s="152"/>
       <c r="H70" s="9" t="s">
         <v>23</v>
       </c>
@@ -10312,9 +10312,9 @@
       <c r="J70" s="7"/>
     </row>
     <row r="71" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A71" s="146"/>
-      <c r="B71" s="146"/>
-      <c r="C71" s="146"/>
+      <c r="A71" s="152"/>
+      <c r="B71" s="152"/>
+      <c r="C71" s="152"/>
       <c r="D71" s="8">
         <v>4</v>
       </c>
@@ -10324,7 +10324,7 @@
       <c r="F71" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G71" s="146"/>
+      <c r="G71" s="152"/>
       <c r="H71" s="9" t="s">
         <v>23</v>
       </c>
@@ -10332,9 +10332,9 @@
       <c r="J71" s="7"/>
     </row>
     <row r="72" spans="1:10" ht="21" customHeight="1">
-      <c r="A72" s="147"/>
-      <c r="B72" s="147"/>
-      <c r="C72" s="147"/>
+      <c r="A72" s="153"/>
+      <c r="B72" s="153"/>
+      <c r="C72" s="153"/>
       <c r="D72" s="8">
         <v>7</v>
       </c>
@@ -10344,7 +10344,7 @@
       <c r="F72" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G72" s="147"/>
+      <c r="G72" s="153"/>
       <c r="H72" s="9" t="s">
         <v>23</v>
       </c>
@@ -10352,7 +10352,7 @@
       <c r="J72" s="7"/>
     </row>
     <row r="73" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A73" s="153"/>
+      <c r="A73" s="157"/>
       <c r="B73" s="149"/>
       <c r="C73" s="149"/>
       <c r="D73" s="149"/>
@@ -10364,13 +10364,13 @@
       <c r="J73" s="7"/>
     </row>
     <row r="74" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A74" s="145" t="s">
+      <c r="A74" s="155" t="s">
         <v>83</v>
       </c>
-      <c r="B74" s="145" t="s">
+      <c r="B74" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="C74" s="145" t="s">
+      <c r="C74" s="155" t="s">
         <v>88</v>
       </c>
       <c r="D74" s="8">
@@ -10382,7 +10382,7 @@
       <c r="F74" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G74" s="152">
+      <c r="G74" s="154">
         <v>23</v>
       </c>
       <c r="H74" s="9" t="s">
@@ -10392,9 +10392,9 @@
       <c r="J74" s="7"/>
     </row>
     <row r="75" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A75" s="146"/>
-      <c r="B75" s="146"/>
-      <c r="C75" s="146"/>
+      <c r="A75" s="152"/>
+      <c r="B75" s="152"/>
+      <c r="C75" s="152"/>
       <c r="D75" s="8">
         <v>2</v>
       </c>
@@ -10404,7 +10404,7 @@
       <c r="F75" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G75" s="146"/>
+      <c r="G75" s="152"/>
       <c r="H75" s="9" t="s">
         <v>23</v>
       </c>
@@ -10412,9 +10412,9 @@
       <c r="J75" s="7"/>
     </row>
     <row r="76" spans="1:10" ht="18" customHeight="1">
-      <c r="A76" s="146"/>
-      <c r="B76" s="146"/>
-      <c r="C76" s="146"/>
+      <c r="A76" s="152"/>
+      <c r="B76" s="152"/>
+      <c r="C76" s="152"/>
       <c r="D76" s="8">
         <v>5</v>
       </c>
@@ -10424,7 +10424,7 @@
       <c r="F76" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="G76" s="146"/>
+      <c r="G76" s="152"/>
       <c r="H76" s="9" t="s">
         <v>23</v>
       </c>
@@ -10432,9 +10432,9 @@
       <c r="J76" s="7"/>
     </row>
     <row r="77" spans="1:10" ht="18.75" customHeight="1">
-      <c r="A77" s="146"/>
-      <c r="B77" s="146"/>
-      <c r="C77" s="146"/>
+      <c r="A77" s="152"/>
+      <c r="B77" s="152"/>
+      <c r="C77" s="152"/>
       <c r="D77" s="8">
         <v>6</v>
       </c>
@@ -10444,7 +10444,7 @@
       <c r="F77" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G77" s="146"/>
+      <c r="G77" s="152"/>
       <c r="H77" s="9" t="s">
         <v>23</v>
       </c>
@@ -10452,9 +10452,9 @@
       <c r="J77" s="7"/>
     </row>
     <row r="78" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A78" s="147"/>
-      <c r="B78" s="147"/>
-      <c r="C78" s="147"/>
+      <c r="A78" s="153"/>
+      <c r="B78" s="153"/>
+      <c r="C78" s="153"/>
       <c r="D78" s="8">
         <v>7</v>
       </c>
@@ -10464,7 +10464,7 @@
       <c r="F78" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G78" s="147"/>
+      <c r="G78" s="153"/>
       <c r="H78" s="9" t="s">
         <v>23</v>
       </c>
@@ -10472,7 +10472,7 @@
       <c r="J78" s="7"/>
     </row>
     <row r="79" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A79" s="153"/>
+      <c r="A79" s="157"/>
       <c r="B79" s="149"/>
       <c r="C79" s="149"/>
       <c r="D79" s="149"/>
@@ -10484,13 +10484,13 @@
       <c r="J79" s="7"/>
     </row>
     <row r="80" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A80" s="145" t="s">
+      <c r="A80" s="155" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="145" t="s">
+      <c r="B80" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="C80" s="145" t="s">
+      <c r="C80" s="155" t="s">
         <v>93</v>
       </c>
       <c r="D80" s="8">
@@ -10502,7 +10502,7 @@
       <c r="F80" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G80" s="152">
+      <c r="G80" s="154">
         <v>119</v>
       </c>
       <c r="H80" s="9" t="s">
@@ -10512,9 +10512,9 @@
       <c r="J80" s="7"/>
     </row>
     <row r="81" spans="1:10" ht="23.25" customHeight="1">
-      <c r="A81" s="146"/>
-      <c r="B81" s="146"/>
-      <c r="C81" s="146"/>
+      <c r="A81" s="152"/>
+      <c r="B81" s="152"/>
+      <c r="C81" s="152"/>
       <c r="D81" s="8">
         <v>2</v>
       </c>
@@ -10524,7 +10524,7 @@
       <c r="F81" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G81" s="146"/>
+      <c r="G81" s="152"/>
       <c r="H81" s="9" t="s">
         <v>23</v>
       </c>
@@ -10532,9 +10532,9 @@
       <c r="J81" s="7"/>
     </row>
     <row r="82" spans="1:10" ht="24" customHeight="1">
-      <c r="A82" s="146"/>
-      <c r="B82" s="146"/>
-      <c r="C82" s="146"/>
+      <c r="A82" s="152"/>
+      <c r="B82" s="152"/>
+      <c r="C82" s="152"/>
       <c r="D82" s="8">
         <v>3</v>
       </c>
@@ -10544,7 +10544,7 @@
       <c r="F82" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="G82" s="146"/>
+      <c r="G82" s="152"/>
       <c r="H82" s="9" t="s">
         <v>23</v>
       </c>
@@ -10554,9 +10554,9 @@
       </c>
     </row>
     <row r="83" spans="1:10" ht="24" customHeight="1">
-      <c r="A83" s="146"/>
-      <c r="B83" s="146"/>
-      <c r="C83" s="146"/>
+      <c r="A83" s="152"/>
+      <c r="B83" s="152"/>
+      <c r="C83" s="152"/>
       <c r="D83" s="8">
         <v>4</v>
       </c>
@@ -10566,7 +10566,7 @@
       <c r="F83" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G83" s="146"/>
+      <c r="G83" s="152"/>
       <c r="H83" s="9" t="s">
         <v>23</v>
       </c>
@@ -10574,9 +10574,9 @@
       <c r="J83" s="7"/>
     </row>
     <row r="84" spans="1:10" ht="27" customHeight="1">
-      <c r="A84" s="147"/>
-      <c r="B84" s="147"/>
-      <c r="C84" s="147"/>
+      <c r="A84" s="153"/>
+      <c r="B84" s="153"/>
+      <c r="C84" s="153"/>
       <c r="D84" s="8">
         <v>7</v>
       </c>
@@ -10586,7 +10586,7 @@
       <c r="F84" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G84" s="147"/>
+      <c r="G84" s="153"/>
       <c r="H84" s="9" t="s">
         <v>23</v>
       </c>
@@ -10624,13 +10624,13 @@
       <c r="J85" s="7"/>
     </row>
     <row r="86" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A86" s="145" t="s">
+      <c r="A86" s="155" t="s">
         <v>99</v>
       </c>
-      <c r="B86" s="145" t="s">
+      <c r="B86" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C86" s="145" t="s">
+      <c r="C86" s="155" t="s">
         <v>100</v>
       </c>
       <c r="D86" s="8">
@@ -10642,7 +10642,7 @@
       <c r="F86" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G86" s="152">
+      <c r="G86" s="154">
         <v>719</v>
       </c>
       <c r="H86" s="9" t="s">
@@ -10652,9 +10652,9 @@
       <c r="J86" s="7"/>
     </row>
     <row r="87" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A87" s="146"/>
-      <c r="B87" s="146"/>
-      <c r="C87" s="146"/>
+      <c r="A87" s="152"/>
+      <c r="B87" s="152"/>
+      <c r="C87" s="152"/>
       <c r="D87" s="8">
         <v>2</v>
       </c>
@@ -10664,7 +10664,7 @@
       <c r="F87" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G87" s="146"/>
+      <c r="G87" s="152"/>
       <c r="H87" s="9" t="s">
         <v>23</v>
       </c>
@@ -10674,9 +10674,9 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A88" s="146"/>
-      <c r="B88" s="146"/>
-      <c r="C88" s="146"/>
+      <c r="A88" s="152"/>
+      <c r="B88" s="152"/>
+      <c r="C88" s="152"/>
       <c r="D88" s="8">
         <v>3</v>
       </c>
@@ -10686,7 +10686,7 @@
       <c r="F88" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="G88" s="146"/>
+      <c r="G88" s="152"/>
       <c r="H88" s="9" t="s">
         <v>23</v>
       </c>
@@ -10694,9 +10694,9 @@
       <c r="J88" s="7"/>
     </row>
     <row r="89" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A89" s="147"/>
-      <c r="B89" s="147"/>
-      <c r="C89" s="147"/>
+      <c r="A89" s="153"/>
+      <c r="B89" s="153"/>
+      <c r="C89" s="153"/>
       <c r="D89" s="8">
         <v>4</v>
       </c>
@@ -10706,7 +10706,7 @@
       <c r="F89" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G89" s="147"/>
+      <c r="G89" s="153"/>
       <c r="H89" s="9" t="s">
         <v>23</v>
       </c>
@@ -10744,13 +10744,13 @@
       <c r="J90" s="7"/>
     </row>
     <row r="91" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A91" s="145" t="s">
+      <c r="A91" s="155" t="s">
         <v>111</v>
       </c>
-      <c r="B91" s="145" t="s">
+      <c r="B91" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C91" s="145" t="s">
+      <c r="C91" s="155" t="s">
         <v>113</v>
       </c>
       <c r="D91" s="8">
@@ -10762,7 +10762,7 @@
       <c r="F91" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G91" s="152">
+      <c r="G91" s="154">
         <v>95</v>
       </c>
       <c r="H91" s="9" t="s">
@@ -10772,9 +10772,9 @@
       <c r="J91" s="7"/>
     </row>
     <row r="92" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A92" s="146"/>
-      <c r="B92" s="146"/>
-      <c r="C92" s="146"/>
+      <c r="A92" s="152"/>
+      <c r="B92" s="152"/>
+      <c r="C92" s="152"/>
       <c r="D92" s="8">
         <v>2</v>
       </c>
@@ -10784,7 +10784,7 @@
       <c r="F92" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G92" s="146"/>
+      <c r="G92" s="152"/>
       <c r="H92" s="9" t="s">
         <v>23</v>
       </c>
@@ -10792,9 +10792,9 @@
       <c r="J92" s="7"/>
     </row>
     <row r="93" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A93" s="146"/>
-      <c r="B93" s="146"/>
-      <c r="C93" s="146"/>
+      <c r="A93" s="152"/>
+      <c r="B93" s="152"/>
+      <c r="C93" s="152"/>
       <c r="D93" s="8">
         <v>3</v>
       </c>
@@ -10804,7 +10804,7 @@
       <c r="F93" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="G93" s="146"/>
+      <c r="G93" s="152"/>
       <c r="H93" s="9" t="s">
         <v>23</v>
       </c>
@@ -10814,9 +10814,9 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A94" s="146"/>
-      <c r="B94" s="146"/>
-      <c r="C94" s="146"/>
+      <c r="A94" s="152"/>
+      <c r="B94" s="152"/>
+      <c r="C94" s="152"/>
       <c r="D94" s="8">
         <v>4</v>
       </c>
@@ -10826,7 +10826,7 @@
       <c r="F94" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G94" s="146"/>
+      <c r="G94" s="152"/>
       <c r="H94" s="9" t="s">
         <v>23</v>
       </c>
@@ -10834,9 +10834,9 @@
       <c r="J94" s="7"/>
     </row>
     <row r="95" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A95" s="147"/>
-      <c r="B95" s="147"/>
-      <c r="C95" s="147"/>
+      <c r="A95" s="153"/>
+      <c r="B95" s="153"/>
+      <c r="C95" s="153"/>
       <c r="D95" s="8">
         <v>10</v>
       </c>
@@ -10846,7 +10846,7 @@
       <c r="F95" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G95" s="147"/>
+      <c r="G95" s="153"/>
       <c r="H95" s="9" t="s">
         <v>23</v>
       </c>
@@ -10884,13 +10884,13 @@
       <c r="J96" s="7"/>
     </row>
     <row r="97" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A97" s="145" t="s">
+      <c r="A97" s="155" t="s">
         <v>118</v>
       </c>
-      <c r="B97" s="145" t="s">
+      <c r="B97" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C97" s="145" t="s">
+      <c r="C97" s="155" t="s">
         <v>119</v>
       </c>
       <c r="D97" s="8">
@@ -10902,7 +10902,7 @@
       <c r="F97" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G97" s="152">
+      <c r="G97" s="154">
         <v>287</v>
       </c>
       <c r="H97" s="9" t="s">
@@ -10912,9 +10912,9 @@
       <c r="J97" s="7"/>
     </row>
     <row r="98" spans="1:10" ht="24.75" customHeight="1">
-      <c r="A98" s="146"/>
-      <c r="B98" s="146"/>
-      <c r="C98" s="146"/>
+      <c r="A98" s="152"/>
+      <c r="B98" s="152"/>
+      <c r="C98" s="152"/>
       <c r="D98" s="8">
         <v>2</v>
       </c>
@@ -10924,7 +10924,7 @@
       <c r="F98" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G98" s="146"/>
+      <c r="G98" s="152"/>
       <c r="H98" s="9" t="s">
         <v>23</v>
       </c>
@@ -10932,9 +10932,9 @@
       <c r="J98" s="7"/>
     </row>
     <row r="99" spans="1:10" ht="24" customHeight="1">
-      <c r="A99" s="146"/>
-      <c r="B99" s="146"/>
-      <c r="C99" s="146"/>
+      <c r="A99" s="152"/>
+      <c r="B99" s="152"/>
+      <c r="C99" s="152"/>
       <c r="D99" s="8">
         <v>3</v>
       </c>
@@ -10944,7 +10944,7 @@
       <c r="F99" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G99" s="146"/>
+      <c r="G99" s="152"/>
       <c r="H99" s="9" t="s">
         <v>23</v>
       </c>
@@ -10952,9 +10952,9 @@
       <c r="J99" s="7"/>
     </row>
     <row r="100" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A100" s="147"/>
-      <c r="B100" s="147"/>
-      <c r="C100" s="147"/>
+      <c r="A100" s="153"/>
+      <c r="B100" s="153"/>
+      <c r="C100" s="153"/>
       <c r="D100" s="8">
         <v>4</v>
       </c>
@@ -10964,7 +10964,7 @@
       <c r="F100" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G100" s="147"/>
+      <c r="G100" s="153"/>
       <c r="H100" s="9" t="s">
         <v>23</v>
       </c>
@@ -11002,13 +11002,13 @@
       <c r="J101" s="7"/>
     </row>
     <row r="102" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A102" s="145" t="s">
+      <c r="A102" s="155" t="s">
         <v>123</v>
       </c>
-      <c r="B102" s="145" t="s">
+      <c r="B102" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C102" s="145" t="s">
+      <c r="C102" s="155" t="s">
         <v>124</v>
       </c>
       <c r="D102" s="8">
@@ -11020,7 +11020,7 @@
       <c r="F102" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="G102" s="152">
+      <c r="G102" s="154">
         <v>119</v>
       </c>
       <c r="H102" s="9" t="s">
@@ -11030,9 +11030,9 @@
       <c r="J102" s="7"/>
     </row>
     <row r="103" spans="1:10" ht="44.25" customHeight="1">
-      <c r="A103" s="147"/>
-      <c r="B103" s="147"/>
-      <c r="C103" s="147"/>
+      <c r="A103" s="153"/>
+      <c r="B103" s="153"/>
+      <c r="C103" s="153"/>
       <c r="D103" s="8">
         <v>2</v>
       </c>
@@ -11042,7 +11042,7 @@
       <c r="F103" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G103" s="147"/>
+      <c r="G103" s="153"/>
       <c r="H103" s="9" t="s">
         <v>23</v>
       </c>
@@ -11062,13 +11062,13 @@
       <c r="J104" s="7"/>
     </row>
     <row r="105" spans="1:10" ht="27" customHeight="1">
-      <c r="A105" s="145" t="s">
+      <c r="A105" s="155" t="s">
         <v>123</v>
       </c>
-      <c r="B105" s="145" t="s">
+      <c r="B105" s="155" t="s">
         <v>35</v>
       </c>
-      <c r="C105" s="145" t="s">
+      <c r="C105" s="155" t="s">
         <v>127</v>
       </c>
       <c r="D105" s="8">
@@ -11080,7 +11080,7 @@
       <c r="F105" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G105" s="152">
+      <c r="G105" s="154">
         <v>239</v>
       </c>
       <c r="H105" s="9" t="s">
@@ -11090,9 +11090,9 @@
       <c r="J105" s="7"/>
     </row>
     <row r="106" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A106" s="146"/>
-      <c r="B106" s="146"/>
-      <c r="C106" s="146"/>
+      <c r="A106" s="152"/>
+      <c r="B106" s="152"/>
+      <c r="C106" s="152"/>
       <c r="D106" s="8">
         <v>2</v>
       </c>
@@ -11102,7 +11102,7 @@
       <c r="F106" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G106" s="146"/>
+      <c r="G106" s="152"/>
       <c r="H106" s="9" t="s">
         <v>23</v>
       </c>
@@ -11110,9 +11110,9 @@
       <c r="J106" s="7"/>
     </row>
     <row r="107" spans="1:10" ht="27" customHeight="1">
-      <c r="A107" s="146"/>
-      <c r="B107" s="146"/>
-      <c r="C107" s="146"/>
+      <c r="A107" s="152"/>
+      <c r="B107" s="152"/>
+      <c r="C107" s="152"/>
       <c r="D107" s="8">
         <v>3</v>
       </c>
@@ -11122,7 +11122,7 @@
       <c r="F107" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="G107" s="146"/>
+      <c r="G107" s="152"/>
       <c r="H107" s="9" t="s">
         <v>23</v>
       </c>
@@ -11130,9 +11130,9 @@
       <c r="J107" s="7"/>
     </row>
     <row r="108" spans="1:10" ht="24.75" customHeight="1">
-      <c r="A108" s="147"/>
-      <c r="B108" s="147"/>
-      <c r="C108" s="147"/>
+      <c r="A108" s="153"/>
+      <c r="B108" s="153"/>
+      <c r="C108" s="153"/>
       <c r="D108" s="8">
         <v>4</v>
       </c>
@@ -11142,7 +11142,7 @@
       <c r="F108" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G108" s="147"/>
+      <c r="G108" s="153"/>
       <c r="H108" s="9" t="s">
         <v>23</v>
       </c>
@@ -14721,6 +14721,76 @@
     </row>
   </sheetData>
   <mergeCells count="86">
+    <mergeCell ref="A44:A48"/>
+    <mergeCell ref="B44:B48"/>
+    <mergeCell ref="C44:C48"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A50:A54"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="G50:G54"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A56:A60"/>
+    <mergeCell ref="B56:B60"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="G56:G60"/>
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="G62:G66"/>
+    <mergeCell ref="G74:G78"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="C62:C66"/>
+    <mergeCell ref="A68:A72"/>
+    <mergeCell ref="B68:B72"/>
+    <mergeCell ref="C68:C72"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A74:A78"/>
+    <mergeCell ref="B74:B78"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="B80:B84"/>
+    <mergeCell ref="C80:C84"/>
+    <mergeCell ref="G80:G84"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="G86:G89"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="A105:A108"/>
+    <mergeCell ref="B105:B108"/>
+    <mergeCell ref="C105:C108"/>
+    <mergeCell ref="G97:G100"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="G105:G108"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="C97:C100"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="A91:A95"/>
+    <mergeCell ref="B91:B95"/>
+    <mergeCell ref="C91:C95"/>
+    <mergeCell ref="G91:G95"/>
+    <mergeCell ref="A97:A100"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C8:C12"/>
+    <mergeCell ref="A26:A30"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="C20:C24"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A43:I43"/>
     <mergeCell ref="G44:G48"/>
     <mergeCell ref="G68:G72"/>
@@ -14737,76 +14807,6 @@
     <mergeCell ref="A38:A42"/>
     <mergeCell ref="B38:B42"/>
     <mergeCell ref="C38:C42"/>
-    <mergeCell ref="A26:A30"/>
-    <mergeCell ref="B26:B30"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="C20:C24"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="C8:C12"/>
-    <mergeCell ref="A91:A95"/>
-    <mergeCell ref="B91:B95"/>
-    <mergeCell ref="C91:C95"/>
-    <mergeCell ref="G91:G95"/>
-    <mergeCell ref="A97:A100"/>
-    <mergeCell ref="A105:A108"/>
-    <mergeCell ref="B105:B108"/>
-    <mergeCell ref="C105:C108"/>
-    <mergeCell ref="G97:G100"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="G105:G108"/>
-    <mergeCell ref="B97:B100"/>
-    <mergeCell ref="C97:C100"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="B80:B84"/>
-    <mergeCell ref="C80:C84"/>
-    <mergeCell ref="G80:G84"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="G86:G89"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="A62:A66"/>
-    <mergeCell ref="G62:G66"/>
-    <mergeCell ref="G74:G78"/>
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="B62:B66"/>
-    <mergeCell ref="C62:C66"/>
-    <mergeCell ref="A68:A72"/>
-    <mergeCell ref="B68:B72"/>
-    <mergeCell ref="C68:C72"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A74:A78"/>
-    <mergeCell ref="B74:B78"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A56:A60"/>
-    <mergeCell ref="B56:B60"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="G56:G60"/>
-    <mergeCell ref="A44:A48"/>
-    <mergeCell ref="B44:B48"/>
-    <mergeCell ref="C44:C48"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A50:A54"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="G50:G54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -14832,10 +14832,10 @@
     </row>
     <row r="2" spans="1:48" ht="69.75" customHeight="1">
       <c r="A2" s="2"/>
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="159"/>
+      <c r="C2" s="162"/>
       <c r="D2" s="4"/>
       <c r="E2" s="5">
         <v>41500</v>
@@ -15015,7 +15015,7 @@
       <c r="AU3" s="21"/>
     </row>
     <row r="4" spans="1:48" ht="14.25">
-      <c r="B4" s="160" t="s">
+      <c r="B4" s="163" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="22" t="s">
@@ -15067,7 +15067,7 @@
       <c r="AU4" s="28"/>
     </row>
     <row r="5" spans="1:48" ht="14.25">
-      <c r="B5" s="161"/>
+      <c r="B5" s="164"/>
       <c r="C5" s="29" t="s">
         <v>42</v>
       </c>
@@ -15117,7 +15117,7 @@
       <c r="AU5" s="13"/>
     </row>
     <row r="6" spans="1:48" ht="14.25">
-      <c r="B6" s="161"/>
+      <c r="B6" s="164"/>
       <c r="C6" s="29" t="s">
         <v>47</v>
       </c>
@@ -15167,7 +15167,7 @@
       <c r="AU6" s="13"/>
     </row>
     <row r="7" spans="1:48" ht="14.25">
-      <c r="B7" s="161"/>
+      <c r="B7" s="164"/>
       <c r="C7" s="29" t="s">
         <v>49</v>
       </c>
@@ -15217,7 +15217,7 @@
       <c r="AU7" s="13"/>
     </row>
     <row r="8" spans="1:48" ht="14.25">
-      <c r="B8" s="161"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="29" t="s">
         <v>52</v>
       </c>
@@ -15267,7 +15267,7 @@
       <c r="AU8" s="13"/>
     </row>
     <row r="9" spans="1:48" ht="14.25">
-      <c r="B9" s="161"/>
+      <c r="B9" s="164"/>
       <c r="C9" s="29" t="s">
         <v>56</v>
       </c>
@@ -15317,7 +15317,7 @@
       <c r="AU9" s="13"/>
     </row>
     <row r="10" spans="1:48" ht="14.25">
-      <c r="B10" s="161"/>
+      <c r="B10" s="164"/>
       <c r="C10" s="29" t="s">
         <v>59</v>
       </c>
@@ -15367,7 +15367,7 @@
       <c r="AU10" s="13"/>
     </row>
     <row r="11" spans="1:48" ht="14.25">
-      <c r="B11" s="161"/>
+      <c r="B11" s="164"/>
       <c r="C11" s="29" t="s">
         <v>63</v>
       </c>
@@ -15417,7 +15417,7 @@
       <c r="AU11" s="13"/>
     </row>
     <row r="12" spans="1:48" ht="14.25">
-      <c r="B12" s="161"/>
+      <c r="B12" s="164"/>
       <c r="C12" s="29" t="s">
         <v>65</v>
       </c>
@@ -15467,7 +15467,7 @@
       <c r="AU12" s="13"/>
     </row>
     <row r="13" spans="1:48" ht="14.25">
-      <c r="B13" s="161"/>
+      <c r="B13" s="164"/>
       <c r="C13" s="29" t="s">
         <v>67</v>
       </c>
@@ -15517,7 +15517,7 @@
       <c r="AU13" s="13"/>
     </row>
     <row r="14" spans="1:48" ht="14.25">
-      <c r="B14" s="161"/>
+      <c r="B14" s="164"/>
       <c r="C14" s="29" t="s">
         <v>69</v>
       </c>
@@ -15567,7 +15567,7 @@
       <c r="AU14" s="13"/>
     </row>
     <row r="15" spans="1:48" ht="14.25">
-      <c r="B15" s="161"/>
+      <c r="B15" s="164"/>
       <c r="C15" s="29" t="s">
         <v>71</v>
       </c>
@@ -15617,7 +15617,7 @@
       <c r="AU15" s="13"/>
     </row>
     <row r="16" spans="1:48" ht="14.25">
-      <c r="B16" s="161"/>
+      <c r="B16" s="164"/>
       <c r="C16" s="29" t="s">
         <v>73</v>
       </c>
@@ -15667,7 +15667,7 @@
       <c r="AU16" s="13"/>
     </row>
     <row r="17" spans="2:47" ht="14.25">
-      <c r="B17" s="161"/>
+      <c r="B17" s="164"/>
       <c r="C17" s="29" t="s">
         <v>75</v>
       </c>
@@ -15717,7 +15717,7 @@
       <c r="AU17" s="13"/>
     </row>
     <row r="18" spans="2:47" ht="14.25">
-      <c r="B18" s="162"/>
+      <c r="B18" s="165"/>
       <c r="C18" s="45" t="s">
         <v>78</v>
       </c>
@@ -15767,7 +15767,7 @@
       <c r="AU18" s="13"/>
     </row>
     <row r="19" spans="2:47" ht="14.25">
-      <c r="B19" s="160" t="s">
+      <c r="B19" s="163" t="s">
         <v>81</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -15819,7 +15819,7 @@
       <c r="AU19" s="13"/>
     </row>
     <row r="20" spans="2:47" ht="14.25">
-      <c r="B20" s="161"/>
+      <c r="B20" s="164"/>
       <c r="C20" s="29" t="s">
         <v>85</v>
       </c>
@@ -15869,7 +15869,7 @@
       <c r="AU20" s="13"/>
     </row>
     <row r="21" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B21" s="161"/>
+      <c r="B21" s="164"/>
       <c r="C21" s="29" t="s">
         <v>87</v>
       </c>
@@ -15919,7 +15919,7 @@
       <c r="AU21" s="13"/>
     </row>
     <row r="22" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B22" s="161"/>
+      <c r="B22" s="164"/>
       <c r="C22" s="29" t="s">
         <v>90</v>
       </c>
@@ -15969,7 +15969,7 @@
       <c r="AU22" s="13"/>
     </row>
     <row r="23" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B23" s="161"/>
+      <c r="B23" s="164"/>
       <c r="C23" s="29" t="s">
         <v>91</v>
       </c>
@@ -16019,7 +16019,7 @@
       <c r="AU23" s="13"/>
     </row>
     <row r="24" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B24" s="161"/>
+      <c r="B24" s="164"/>
       <c r="C24" s="29" t="s">
         <v>92</v>
       </c>
@@ -16069,7 +16069,7 @@
       <c r="AU24" s="13"/>
     </row>
     <row r="25" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B25" s="161"/>
+      <c r="B25" s="164"/>
       <c r="C25" s="29" t="s">
         <v>94</v>
       </c>
@@ -16119,7 +16119,7 @@
       <c r="AU25" s="13"/>
     </row>
     <row r="26" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B26" s="161"/>
+      <c r="B26" s="164"/>
       <c r="C26" s="29" t="s">
         <v>97</v>
       </c>
@@ -16169,7 +16169,7 @@
       <c r="AU26" s="13"/>
     </row>
     <row r="27" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B27" s="161"/>
+      <c r="B27" s="164"/>
       <c r="C27" s="29" t="s">
         <v>98</v>
       </c>
@@ -16219,7 +16219,7 @@
       <c r="AU27" s="13"/>
     </row>
     <row r="28" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B28" s="161"/>
+      <c r="B28" s="164"/>
       <c r="C28" s="29" t="s">
         <v>102</v>
       </c>
@@ -16269,7 +16269,7 @@
       <c r="AU28" s="13"/>
     </row>
     <row r="29" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B29" s="161"/>
+      <c r="B29" s="164"/>
       <c r="C29" s="29" t="s">
         <v>104</v>
       </c>
@@ -16319,7 +16319,7 @@
       <c r="AU29" s="13"/>
     </row>
     <row r="30" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B30" s="162"/>
+      <c r="B30" s="165"/>
       <c r="C30" s="45" t="s">
         <v>109</v>
       </c>
@@ -16369,7 +16369,7 @@
       <c r="AU30" s="13"/>
     </row>
     <row r="31" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B31" s="163" t="s">
+      <c r="B31" s="166" t="s">
         <v>110</v>
       </c>
       <c r="C31" s="53" t="s">
@@ -16421,7 +16421,7 @@
       <c r="AU31" s="13"/>
     </row>
     <row r="32" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B32" s="156"/>
+      <c r="B32" s="159"/>
       <c r="C32" s="54" t="s">
         <v>114</v>
       </c>
@@ -16471,7 +16471,7 @@
       <c r="AU32" s="13"/>
     </row>
     <row r="33" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B33" s="156"/>
+      <c r="B33" s="159"/>
       <c r="C33" s="54" t="s">
         <v>116</v>
       </c>
@@ -16521,7 +16521,7 @@
       <c r="AU33" s="13"/>
     </row>
     <row r="34" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B34" s="156"/>
+      <c r="B34" s="159"/>
       <c r="C34" s="54" t="s">
         <v>117</v>
       </c>
@@ -16571,7 +16571,7 @@
       <c r="AU34" s="13"/>
     </row>
     <row r="35" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B35" s="156"/>
+      <c r="B35" s="159"/>
       <c r="C35" s="54" t="s">
         <v>120</v>
       </c>
@@ -16621,7 +16621,7 @@
       <c r="AU35" s="13"/>
     </row>
     <row r="36" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B36" s="156"/>
+      <c r="B36" s="159"/>
       <c r="C36" s="56" t="s">
         <v>122</v>
       </c>
@@ -16671,7 +16671,7 @@
       <c r="AU36" s="13"/>
     </row>
     <row r="37" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B37" s="156"/>
+      <c r="B37" s="159"/>
       <c r="C37" s="58" t="s">
         <v>126</v>
       </c>
@@ -16721,7 +16721,7 @@
       <c r="AU37" s="13"/>
     </row>
     <row r="38" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B38" s="156"/>
+      <c r="B38" s="159"/>
       <c r="C38" s="60" t="s">
         <v>128</v>
       </c>
@@ -16771,7 +16771,7 @@
       <c r="AU38" s="13"/>
     </row>
     <row r="39" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B39" s="156"/>
+      <c r="B39" s="159"/>
       <c r="C39" s="60" t="s">
         <v>130</v>
       </c>
@@ -16821,7 +16821,7 @@
       <c r="AU39" s="13"/>
     </row>
     <row r="40" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B40" s="156"/>
+      <c r="B40" s="159"/>
       <c r="C40" s="62" t="s">
         <v>132</v>
       </c>
@@ -16871,7 +16871,7 @@
       <c r="AU40" s="13"/>
     </row>
     <row r="41" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B41" s="156"/>
+      <c r="B41" s="159"/>
       <c r="C41" s="63" t="s">
         <v>133</v>
       </c>
@@ -16921,7 +16921,7 @@
       <c r="AU41" s="13"/>
     </row>
     <row r="42" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B42" s="156"/>
+      <c r="B42" s="159"/>
       <c r="C42" s="64" t="s">
         <v>134</v>
       </c>
@@ -16971,7 +16971,7 @@
       <c r="AU42" s="13"/>
     </row>
     <row r="43" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B43" s="156"/>
+      <c r="B43" s="159"/>
       <c r="C43" s="65" t="s">
         <v>135</v>
       </c>
@@ -17021,7 +17021,7 @@
       <c r="AU43" s="13"/>
     </row>
     <row r="44" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B44" s="156"/>
+      <c r="B44" s="159"/>
       <c r="C44" s="66" t="s">
         <v>136</v>
       </c>
@@ -17071,7 +17071,7 @@
       <c r="AU44" s="13"/>
     </row>
     <row r="45" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B45" s="156"/>
+      <c r="B45" s="159"/>
       <c r="C45" s="67" t="s">
         <v>137</v>
       </c>
@@ -17121,7 +17121,7 @@
       <c r="AU45" s="13"/>
     </row>
     <row r="46" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B46" s="156"/>
+      <c r="B46" s="159"/>
       <c r="C46" s="68" t="s">
         <v>138</v>
       </c>
@@ -17171,7 +17171,7 @@
       <c r="AU46" s="13"/>
     </row>
     <row r="47" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B47" s="156"/>
+      <c r="B47" s="159"/>
       <c r="C47" s="69" t="s">
         <v>139</v>
       </c>
@@ -17221,7 +17221,7 @@
       <c r="AU47" s="13"/>
     </row>
     <row r="48" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B48" s="156"/>
+      <c r="B48" s="159"/>
       <c r="C48" s="70" t="s">
         <v>140</v>
       </c>
@@ -17271,7 +17271,7 @@
       <c r="AU48" s="13"/>
     </row>
     <row r="49" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B49" s="157"/>
+      <c r="B49" s="160"/>
       <c r="C49" s="71" t="s">
         <v>141</v>
       </c>
@@ -17321,7 +17321,7 @@
       <c r="AU49" s="13"/>
     </row>
     <row r="50" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B50" s="155" t="s">
+      <c r="B50" s="158" t="s">
         <v>142</v>
       </c>
       <c r="C50" s="72" t="s">
@@ -17373,7 +17373,7 @@
       <c r="AU50" s="13"/>
     </row>
     <row r="51" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B51" s="156"/>
+      <c r="B51" s="159"/>
       <c r="C51" s="73" t="s">
         <v>144</v>
       </c>
@@ -17423,7 +17423,7 @@
       <c r="AU51" s="13"/>
     </row>
     <row r="52" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B52" s="156"/>
+      <c r="B52" s="159"/>
       <c r="C52" s="73" t="s">
         <v>145</v>
       </c>
@@ -17473,7 +17473,7 @@
       <c r="AU52" s="13"/>
     </row>
     <row r="53" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B53" s="157"/>
+      <c r="B53" s="160"/>
       <c r="C53" s="74" t="s">
         <v>146</v>
       </c>
@@ -17523,7 +17523,7 @@
       <c r="AU53" s="13"/>
     </row>
     <row r="54" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B54" s="155" t="s">
+      <c r="B54" s="158" t="s">
         <v>147</v>
       </c>
       <c r="C54" s="72" t="s">
@@ -17575,7 +17575,7 @@
       <c r="AU54" s="13"/>
     </row>
     <row r="55" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B55" s="156"/>
+      <c r="B55" s="159"/>
       <c r="C55" s="73" t="s">
         <v>149</v>
       </c>
@@ -17625,7 +17625,7 @@
       <c r="AU55" s="13"/>
     </row>
     <row r="56" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B56" s="156"/>
+      <c r="B56" s="159"/>
       <c r="C56" s="73" t="s">
         <v>150</v>
       </c>
@@ -17675,7 +17675,7 @@
       <c r="AU56" s="87"/>
     </row>
     <row r="57" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B57" s="156"/>
+      <c r="B57" s="159"/>
       <c r="C57" s="73" t="s">
         <v>151</v>
       </c>
@@ -17725,7 +17725,7 @@
       <c r="AU57" s="88"/>
     </row>
     <row r="58" spans="2:47" ht="15.75" customHeight="1">
-      <c r="B58" s="157"/>
+      <c r="B58" s="160"/>
       <c r="C58" s="75" t="s">
         <v>152</v>
       </c>
@@ -20656,10 +20656,10 @@
     </row>
     <row r="2" spans="1:26" ht="14.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="158" t="s">
+      <c r="B2" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="159"/>
+      <c r="C2" s="162"/>
       <c r="D2" s="4"/>
       <c r="E2" s="39" t="s">
         <v>61</v>
@@ -20713,14 +20713,14 @@
       <c r="Y3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="14.25">
-      <c r="B4" s="160" t="s">
+      <c r="B4" s="163" t="s">
         <v>37</v>
       </c>
       <c r="C4" s="22" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="164">
+      <c r="E4" s="167">
         <v>0</v>
       </c>
       <c r="F4" s="42"/>
@@ -20745,12 +20745,12 @@
       <c r="Y4" s="1"/>
     </row>
     <row r="5" spans="1:26" ht="14.25">
-      <c r="B5" s="161"/>
+      <c r="B5" s="164"/>
       <c r="C5" s="29" t="s">
         <v>42</v>
       </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="156"/>
+      <c r="E5" s="159"/>
       <c r="F5" s="42"/>
       <c r="G5" s="42"/>
       <c r="H5" s="42"/>
@@ -20773,12 +20773,12 @@
       <c r="Y5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="14.25">
-      <c r="B6" s="161"/>
+      <c r="B6" s="164"/>
       <c r="C6" s="29" t="s">
         <v>47</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="156"/>
+      <c r="E6" s="159"/>
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
@@ -20801,12 +20801,12 @@
       <c r="Y6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="14.25">
-      <c r="B7" s="161"/>
+      <c r="B7" s="164"/>
       <c r="C7" s="29" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="156"/>
+      <c r="E7" s="159"/>
       <c r="F7" s="42"/>
       <c r="G7" s="42"/>
       <c r="H7" s="42"/>
@@ -20829,12 +20829,12 @@
       <c r="Y7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="14.25">
-      <c r="B8" s="161"/>
+      <c r="B8" s="164"/>
       <c r="C8" s="29" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="165"/>
+      <c r="E8" s="168"/>
       <c r="F8" s="42"/>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
@@ -20857,12 +20857,12 @@
       <c r="Y8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="14.25">
-      <c r="B9" s="161"/>
+      <c r="B9" s="164"/>
       <c r="C9" s="29" t="s">
         <v>56</v>
       </c>
       <c r="D9" s="1"/>
-      <c r="E9" s="166">
+      <c r="E9" s="169">
         <v>1500000</v>
       </c>
       <c r="F9" s="42"/>
@@ -20887,12 +20887,12 @@
       <c r="Y9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="14.25">
-      <c r="B10" s="161"/>
+      <c r="B10" s="164"/>
       <c r="C10" s="29" t="s">
         <v>59</v>
       </c>
       <c r="D10" s="1"/>
-      <c r="E10" s="156"/>
+      <c r="E10" s="159"/>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
@@ -20915,12 +20915,12 @@
       <c r="Y10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="14.25">
-      <c r="B11" s="161"/>
+      <c r="B11" s="164"/>
       <c r="C11" s="29" t="s">
         <v>63</v>
       </c>
       <c r="D11" s="1"/>
-      <c r="E11" s="156"/>
+      <c r="E11" s="159"/>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
@@ -20943,12 +20943,12 @@
       <c r="Y11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="14.25">
-      <c r="B12" s="161"/>
+      <c r="B12" s="164"/>
       <c r="C12" s="29" t="s">
         <v>65</v>
       </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="156"/>
+      <c r="E12" s="159"/>
       <c r="F12" s="42"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
@@ -20971,12 +20971,12 @@
       <c r="Y12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="14.25">
-      <c r="B13" s="161"/>
+      <c r="B13" s="164"/>
       <c r="C13" s="29" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="156"/>
+      <c r="E13" s="159"/>
       <c r="F13" s="42"/>
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
@@ -20999,12 +20999,12 @@
       <c r="Y13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="14.25">
-      <c r="B14" s="161"/>
+      <c r="B14" s="164"/>
       <c r="C14" s="29" t="s">
         <v>69</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="156"/>
+      <c r="E14" s="159"/>
       <c r="F14" s="42"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
@@ -21027,12 +21027,12 @@
       <c r="Y14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="14.25">
-      <c r="B15" s="161"/>
+      <c r="B15" s="164"/>
       <c r="C15" s="29" t="s">
         <v>71</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="156"/>
+      <c r="E15" s="159"/>
       <c r="F15" s="42"/>
       <c r="G15" s="42"/>
       <c r="H15" s="42"/>
@@ -21055,12 +21055,12 @@
       <c r="Y15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="14.25">
-      <c r="B16" s="161"/>
+      <c r="B16" s="164"/>
       <c r="C16" s="29" t="s">
         <v>73</v>
       </c>
       <c r="D16" s="1"/>
-      <c r="E16" s="165"/>
+      <c r="E16" s="168"/>
       <c r="F16" s="42"/>
       <c r="G16" s="42"/>
       <c r="H16" s="42"/>
@@ -21083,12 +21083,12 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" spans="2:25" ht="14.25">
-      <c r="B17" s="161"/>
+      <c r="B17" s="164"/>
       <c r="C17" s="29" t="s">
         <v>75</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="166">
+      <c r="E17" s="169">
         <v>1200000</v>
       </c>
       <c r="F17" s="42"/>
@@ -21113,12 +21113,12 @@
       <c r="Y17" s="1"/>
     </row>
     <row r="18" spans="2:25" ht="14.25">
-      <c r="B18" s="162"/>
+      <c r="B18" s="165"/>
       <c r="C18" s="45" t="s">
         <v>78</v>
       </c>
       <c r="D18" s="1"/>
-      <c r="E18" s="165"/>
+      <c r="E18" s="168"/>
       <c r="F18" s="42"/>
       <c r="G18" s="42"/>
       <c r="H18" s="42"/>
@@ -21141,7 +21141,7 @@
       <c r="Y18" s="1"/>
     </row>
     <row r="19" spans="2:25" ht="14.25">
-      <c r="B19" s="160" t="s">
+      <c r="B19" s="163" t="s">
         <v>81</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -21173,7 +21173,7 @@
       <c r="Y19" s="1"/>
     </row>
     <row r="20" spans="2:25" ht="14.25">
-      <c r="B20" s="161"/>
+      <c r="B20" s="164"/>
       <c r="C20" s="29" t="s">
         <v>85</v>
       </c>
@@ -21203,7 +21203,7 @@
       <c r="Y20" s="1"/>
     </row>
     <row r="21" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B21" s="161"/>
+      <c r="B21" s="164"/>
       <c r="C21" s="29" t="s">
         <v>87</v>
       </c>
@@ -21233,7 +21233,7 @@
       <c r="Y21" s="1"/>
     </row>
     <row r="22" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B22" s="161"/>
+      <c r="B22" s="164"/>
       <c r="C22" s="29" t="s">
         <v>90</v>
       </c>
@@ -21263,7 +21263,7 @@
       <c r="Y22" s="1"/>
     </row>
     <row r="23" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B23" s="161"/>
+      <c r="B23" s="164"/>
       <c r="C23" s="29" t="s">
         <v>91</v>
       </c>
@@ -21293,7 +21293,7 @@
       <c r="Y23" s="1"/>
     </row>
     <row r="24" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B24" s="161"/>
+      <c r="B24" s="164"/>
       <c r="C24" s="29" t="s">
         <v>92</v>
       </c>
@@ -21323,7 +21323,7 @@
       <c r="Y24" s="1"/>
     </row>
     <row r="25" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B25" s="161"/>
+      <c r="B25" s="164"/>
       <c r="C25" s="29" t="s">
         <v>94</v>
       </c>
@@ -21353,7 +21353,7 @@
       <c r="Y25" s="1"/>
     </row>
     <row r="26" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B26" s="161"/>
+      <c r="B26" s="164"/>
       <c r="C26" s="29" t="s">
         <v>97</v>
       </c>
@@ -21383,7 +21383,7 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B27" s="161"/>
+      <c r="B27" s="164"/>
       <c r="C27" s="29" t="s">
         <v>98</v>
       </c>
@@ -21413,7 +21413,7 @@
       <c r="Y27" s="1"/>
     </row>
     <row r="28" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B28" s="161"/>
+      <c r="B28" s="164"/>
       <c r="C28" s="29" t="s">
         <v>102</v>
       </c>
@@ -21443,7 +21443,7 @@
       <c r="Y28" s="1"/>
     </row>
     <row r="29" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B29" s="161"/>
+      <c r="B29" s="164"/>
       <c r="C29" s="29" t="s">
         <v>104</v>
       </c>
@@ -21473,7 +21473,7 @@
       <c r="Y29" s="1"/>
     </row>
     <row r="30" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B30" s="162"/>
+      <c r="B30" s="165"/>
       <c r="C30" s="45" t="s">
         <v>109</v>
       </c>
@@ -21503,14 +21503,14 @@
       <c r="Y30" s="1"/>
     </row>
     <row r="31" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B31" s="163" t="s">
+      <c r="B31" s="166" t="s">
         <v>110</v>
       </c>
       <c r="C31" s="53" t="s">
         <v>112</v>
       </c>
       <c r="D31" s="1"/>
-      <c r="E31" s="166">
+      <c r="E31" s="169">
         <v>6000000</v>
       </c>
       <c r="F31" s="42"/>
@@ -21535,12 +21535,12 @@
       <c r="Y31" s="1"/>
     </row>
     <row r="32" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B32" s="156"/>
+      <c r="B32" s="159"/>
       <c r="C32" s="54" t="s">
         <v>114</v>
       </c>
       <c r="D32" s="1"/>
-      <c r="E32" s="156"/>
+      <c r="E32" s="159"/>
       <c r="F32" s="42"/>
       <c r="G32" s="42"/>
       <c r="H32" s="42"/>
@@ -21563,12 +21563,12 @@
       <c r="Y32" s="1"/>
     </row>
     <row r="33" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B33" s="156"/>
+      <c r="B33" s="159"/>
       <c r="C33" s="54" t="s">
         <v>116</v>
       </c>
       <c r="D33" s="1"/>
-      <c r="E33" s="156"/>
+      <c r="E33" s="159"/>
       <c r="F33" s="42"/>
       <c r="G33" s="42"/>
       <c r="H33" s="42"/>
@@ -21591,12 +21591,12 @@
       <c r="Y33" s="1"/>
     </row>
     <row r="34" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B34" s="156"/>
+      <c r="B34" s="159"/>
       <c r="C34" s="54" t="s">
         <v>117</v>
       </c>
       <c r="D34" s="1"/>
-      <c r="E34" s="156"/>
+      <c r="E34" s="159"/>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
       <c r="H34" s="42"/>
@@ -21619,12 +21619,12 @@
       <c r="Y34" s="1"/>
     </row>
     <row r="35" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B35" s="156"/>
+      <c r="B35" s="159"/>
       <c r="C35" s="54" t="s">
         <v>120</v>
       </c>
       <c r="D35" s="1"/>
-      <c r="E35" s="156"/>
+      <c r="E35" s="159"/>
       <c r="F35" s="42"/>
       <c r="G35" s="42"/>
       <c r="H35" s="42"/>
@@ -21647,12 +21647,12 @@
       <c r="Y35" s="1"/>
     </row>
     <row r="36" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B36" s="156"/>
+      <c r="B36" s="159"/>
       <c r="C36" s="56" t="s">
         <v>122</v>
       </c>
       <c r="D36" s="1"/>
-      <c r="E36" s="156"/>
+      <c r="E36" s="159"/>
       <c r="F36" s="42"/>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
@@ -21675,12 +21675,12 @@
       <c r="Y36" s="1"/>
     </row>
     <row r="37" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B37" s="156"/>
+      <c r="B37" s="159"/>
       <c r="C37" s="58" t="s">
         <v>126</v>
       </c>
       <c r="D37" s="1"/>
-      <c r="E37" s="156"/>
+      <c r="E37" s="159"/>
       <c r="F37" s="42"/>
       <c r="G37" s="42"/>
       <c r="H37" s="42"/>
@@ -21703,12 +21703,12 @@
       <c r="Y37" s="1"/>
     </row>
     <row r="38" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B38" s="156"/>
+      <c r="B38" s="159"/>
       <c r="C38" s="60" t="s">
         <v>128</v>
       </c>
       <c r="D38" s="1"/>
-      <c r="E38" s="156"/>
+      <c r="E38" s="159"/>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
       <c r="H38" s="42"/>
@@ -21731,12 +21731,12 @@
       <c r="Y38" s="1"/>
     </row>
     <row r="39" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B39" s="156"/>
+      <c r="B39" s="159"/>
       <c r="C39" s="60" t="s">
         <v>130</v>
       </c>
       <c r="D39" s="1"/>
-      <c r="E39" s="156"/>
+      <c r="E39" s="159"/>
       <c r="F39" s="42"/>
       <c r="G39" s="42"/>
       <c r="H39" s="42"/>
@@ -21759,12 +21759,12 @@
       <c r="Y39" s="1"/>
     </row>
     <row r="40" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B40" s="156"/>
+      <c r="B40" s="159"/>
       <c r="C40" s="62" t="s">
         <v>132</v>
       </c>
       <c r="D40" s="1"/>
-      <c r="E40" s="156"/>
+      <c r="E40" s="159"/>
       <c r="F40" s="42"/>
       <c r="G40" s="42"/>
       <c r="H40" s="42"/>
@@ -21787,12 +21787,12 @@
       <c r="Y40" s="1"/>
     </row>
     <row r="41" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B41" s="156"/>
+      <c r="B41" s="159"/>
       <c r="C41" s="63" t="s">
         <v>133</v>
       </c>
       <c r="D41" s="1"/>
-      <c r="E41" s="156"/>
+      <c r="E41" s="159"/>
       <c r="F41" s="42"/>
       <c r="G41" s="42"/>
       <c r="H41" s="42"/>
@@ -21815,12 +21815,12 @@
       <c r="Y41" s="1"/>
     </row>
     <row r="42" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B42" s="156"/>
+      <c r="B42" s="159"/>
       <c r="C42" s="64" t="s">
         <v>134</v>
       </c>
       <c r="D42" s="1"/>
-      <c r="E42" s="156"/>
+      <c r="E42" s="159"/>
       <c r="F42" s="42"/>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
@@ -21843,12 +21843,12 @@
       <c r="Y42" s="1"/>
     </row>
     <row r="43" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B43" s="156"/>
+      <c r="B43" s="159"/>
       <c r="C43" s="65" t="s">
         <v>135</v>
       </c>
       <c r="D43" s="1"/>
-      <c r="E43" s="156"/>
+      <c r="E43" s="159"/>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
       <c r="H43" s="42"/>
@@ -21871,12 +21871,12 @@
       <c r="Y43" s="1"/>
     </row>
     <row r="44" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B44" s="156"/>
+      <c r="B44" s="159"/>
       <c r="C44" s="66" t="s">
         <v>136</v>
       </c>
       <c r="D44" s="1"/>
-      <c r="E44" s="156"/>
+      <c r="E44" s="159"/>
       <c r="F44" s="42"/>
       <c r="G44" s="42"/>
       <c r="H44" s="42"/>
@@ -21899,12 +21899,12 @@
       <c r="Y44" s="1"/>
     </row>
     <row r="45" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B45" s="156"/>
+      <c r="B45" s="159"/>
       <c r="C45" s="67" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="1"/>
-      <c r="E45" s="156"/>
+      <c r="E45" s="159"/>
       <c r="F45" s="42"/>
       <c r="G45" s="42"/>
       <c r="H45" s="42"/>
@@ -21927,12 +21927,12 @@
       <c r="Y45" s="1"/>
     </row>
     <row r="46" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B46" s="156"/>
+      <c r="B46" s="159"/>
       <c r="C46" s="68" t="s">
         <v>138</v>
       </c>
       <c r="D46" s="1"/>
-      <c r="E46" s="156"/>
+      <c r="E46" s="159"/>
       <c r="F46" s="42"/>
       <c r="G46" s="42"/>
       <c r="H46" s="42"/>
@@ -21955,12 +21955,12 @@
       <c r="Y46" s="1"/>
     </row>
     <row r="47" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B47" s="156"/>
+      <c r="B47" s="159"/>
       <c r="C47" s="69" t="s">
         <v>139</v>
       </c>
       <c r="D47" s="1"/>
-      <c r="E47" s="156"/>
+      <c r="E47" s="159"/>
       <c r="F47" s="42"/>
       <c r="G47" s="42"/>
       <c r="H47" s="42"/>
@@ -21983,12 +21983,12 @@
       <c r="Y47" s="1"/>
     </row>
     <row r="48" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B48" s="156"/>
+      <c r="B48" s="159"/>
       <c r="C48" s="70" t="s">
         <v>140</v>
       </c>
       <c r="D48" s="1"/>
-      <c r="E48" s="156"/>
+      <c r="E48" s="159"/>
       <c r="F48" s="42"/>
       <c r="G48" s="42"/>
       <c r="H48" s="42"/>
@@ -22011,12 +22011,12 @@
       <c r="Y48" s="1"/>
     </row>
     <row r="49" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B49" s="157"/>
+      <c r="B49" s="160"/>
       <c r="C49" s="71" t="s">
         <v>141</v>
       </c>
       <c r="D49" s="1"/>
-      <c r="E49" s="165"/>
+      <c r="E49" s="168"/>
       <c r="F49" s="42"/>
       <c r="G49" s="42"/>
       <c r="H49" s="42"/>
@@ -22039,7 +22039,7 @@
       <c r="Y49" s="1"/>
     </row>
     <row r="50" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B50" s="155" t="s">
+      <c r="B50" s="158" t="s">
         <v>142</v>
       </c>
       <c r="C50" s="72" t="s">
@@ -22071,7 +22071,7 @@
       <c r="Y50" s="1"/>
     </row>
     <row r="51" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B51" s="156"/>
+      <c r="B51" s="159"/>
       <c r="C51" s="73" t="s">
         <v>144</v>
       </c>
@@ -22101,7 +22101,7 @@
       <c r="Y51" s="1"/>
     </row>
     <row r="52" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B52" s="156"/>
+      <c r="B52" s="159"/>
       <c r="C52" s="73" t="s">
         <v>145</v>
       </c>
@@ -22131,7 +22131,7 @@
       <c r="Y52" s="1"/>
     </row>
     <row r="53" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B53" s="157"/>
+      <c r="B53" s="160"/>
       <c r="C53" s="74" t="s">
         <v>146</v>
       </c>
@@ -22161,7 +22161,7 @@
       <c r="Y53" s="1"/>
     </row>
     <row r="54" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B54" s="155" t="s">
+      <c r="B54" s="158" t="s">
         <v>147</v>
       </c>
       <c r="C54" s="72" t="s">
@@ -22193,7 +22193,7 @@
       <c r="Y54" s="1"/>
     </row>
     <row r="55" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B55" s="156"/>
+      <c r="B55" s="159"/>
       <c r="C55" s="73" t="s">
         <v>149</v>
       </c>
@@ -22223,7 +22223,7 @@
       <c r="Y55" s="1"/>
     </row>
     <row r="56" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B56" s="156"/>
+      <c r="B56" s="159"/>
       <c r="C56" s="73" t="s">
         <v>150</v>
       </c>
@@ -22253,7 +22253,7 @@
       <c r="Y56" s="1"/>
     </row>
     <row r="57" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B57" s="156"/>
+      <c r="B57" s="159"/>
       <c r="C57" s="73" t="s">
         <v>151</v>
       </c>
@@ -22283,7 +22283,7 @@
       <c r="Y57" s="1"/>
     </row>
     <row r="58" spans="2:25" ht="15.75" customHeight="1">
-      <c r="B58" s="157"/>
+      <c r="B58" s="160"/>
       <c r="C58" s="75" t="s">
         <v>152</v>
       </c>
